--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -426,9 +426,19 @@
     <author>case_daily.py</author>
   </authors>
   <commentList>
-    <comment ref="E37" authorId="0" shapeId="0">
+    <comment ref="O37" authorId="0" shapeId="0">
       <text>
-        <t>fn=1 (native_1d) — taker từ Zone-A-agg (ledger_v2 CAMPAIGNS/BANK_20260720)</t>
+        <t>SUSPECT fn&lt;6 (fn=1, src=native_1d)</t>
+      </text>
+    </comment>
+    <comment ref="P37" authorId="0" shapeId="0">
+      <text>
+        <t>SUSPECT fn&lt;6 (fn=1, src=native_1d)</t>
+      </text>
+    </comment>
+    <comment ref="Q37" authorId="0" shapeId="0">
+      <text>
+        <t>SUSPECT fn&lt;6 (fn=1, src=native_1d)</t>
       </text>
     </comment>
   </commentList>
@@ -3366,8 +3376,8 @@
         <f>IFERROR(B37/B36-1,"")</f>
         <v/>
       </c>
-      <c r="E37" t="n">
-        <v>0.5046</v>
+      <c r="E37" s="27" t="n">
+        <v>0.4989226837701057</v>
       </c>
       <c r="F37" s="27" t="n">
         <v>-0.00026779</v>

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -418,31 +418,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>case_daily.py</author>
-  </authors>
-  <commentList>
-    <comment ref="O37" authorId="0" shapeId="0">
-      <text>
-        <t>SUSPECT fn&lt;6 (fn=1, src=native_1d)</t>
-      </text>
-    </comment>
-    <comment ref="P37" authorId="0" shapeId="0">
-      <text>
-        <t>SUSPECT fn&lt;6 (fn=1, src=native_1d)</t>
-      </text>
-    </comment>
-    <comment ref="Q37" authorId="0" shapeId="0">
-      <text>
-        <t>SUSPECT fn&lt;6 (fn=1, src=native_1d)</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -780,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AO37"/>
+  <dimension ref="A1:AO39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="27" min="1" max="1"/>
@@ -3372,27 +3347,33 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="B37" s="27" t="n">
+        <v>0.1713490368477554</v>
+      </c>
       <c r="C37" s="27">
         <f>IFERROR(B37/B36-1,"")</f>
         <v/>
       </c>
+      <c r="D37" s="27" t="n">
+        <v>738355605.75427</v>
+      </c>
       <c r="E37" s="27" t="n">
         <v>0.4989226837701057</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>-0.00026779</v>
+        <v>-0.000988205</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>-0.00026779</v>
+        <v>-0.00205082</v>
       </c>
       <c r="H37" s="27" t="n">
-        <v>-0.00026779</v>
+        <v>-1.461e-05</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L37" s="27" t="n">
-        <v>25000000</v>
+        <v>25365666.16605</v>
       </c>
       <c r="O37" s="27" t="n">
         <v>1.3307</v>
@@ -3425,6 +3406,142 @@
       </c>
       <c r="AJ37" s="27">
         <f>IF(OR(AB37="",D37="",D37=0),"",AB37/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>0.0887329722906726</v>
+      </c>
+      <c r="C38" s="27">
+        <f>IFERROR(B38/B37-1,"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="27" t="n">
+        <v>1039593900.21891</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <v>0.491663277755185</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>-0.003337582</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>-4.97e-05</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L38" s="27" t="n">
+        <v>21421641.72207464</v>
+      </c>
+      <c r="O38" s="27" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="P38" s="27" t="n">
+        <v>0.9346</v>
+      </c>
+      <c r="Q38" s="27" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="R38" s="27">
+        <f>IFERROR(O38/P38,"")</f>
+        <v/>
+      </c>
+      <c r="S38" s="27">
+        <f>IFERROR(AVERAGE(R36:R38),"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="27">
+        <f>IFERROR(Q38/Q33,"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="27">
+        <f>IFERROR(O38/O35-1,"")</f>
+        <v/>
+      </c>
+      <c r="V38" s="27">
+        <f>IFERROR(P38/P35-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="27">
+        <f>IF(OR(AB38="",D38="",D38=0),"",AB38/D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0630603801681764</v>
+      </c>
+      <c r="C39">
+        <f>IFERROR(B39/B38-1,"")</f>
+        <v/>
+      </c>
+      <c r="D39" t="n">
+        <v>562696137.64149</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.491559894244458</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.001911111666666667</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.00438872</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.00069484</v>
+      </c>
+      <c r="I39" t="n">
+        <v>24</v>
+      </c>
+      <c r="L39" t="n">
+        <v>17254036.24131712</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.1095</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.7933</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.5013</v>
+      </c>
+      <c r="R39">
+        <f>IFERROR(O39/P39,"")</f>
+        <v/>
+      </c>
+      <c r="S39">
+        <f>IFERROR(AVERAGE(R37:R39),"")</f>
+        <v/>
+      </c>
+      <c r="T39">
+        <f>IFERROR(Q39/Q34,"")</f>
+        <v/>
+      </c>
+      <c r="U39">
+        <f>IFERROR(O39/O36-1,"")</f>
+        <v/>
+      </c>
+      <c r="V39">
+        <f>IFERROR(P39/P36-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ39">
+        <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
         <v/>
       </c>
     </row>
@@ -3438,7 +3555,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -96,8 +96,11 @@
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +155,11 @@
         <bgColor rgb="FF375623"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4A843"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +195,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -348,6 +356,7 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="27" min="1" max="1"/>
@@ -739,6 +748,216 @@
       <c r="B14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">O vang = operator dien/quyet · Header nau vang (sheet DAILY) = cot manual · Dong to cam (DAILY) = data_bad=1, so mang sai so · Cot cong thuc (ret_1d, div, slope, oi_vs_med14, alpha) tu tinh khi may append dong moi — copy cong thuc dong tren xuong. </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="54">
+        <f>== PROBE-VERIFIED — H1/H2/H3 (04/08/2026) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>px_T0 probe-verified</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.03773 (freshwatch 10/07 px_avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>px_max [1h spike native]</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.67205 USDT — 27/07 06:00 UTC (fapi 1h high, vol 299M USDT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>px_max [daily avg basis]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.37632 USDT — 26/07 freshwatch avg (truoc da dung lam px_max)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>px_max [close basis]</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.41958 USDT — 27/07 close (fapi 1h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>markup T0→spike_high</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>+1681% (0.03773→0.67205)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>markup T0→daily_avg_max</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>+897% (0.03773→0.37632)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OI PRE range (25/06-09/07)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4.31M→4.73M FLAT — khong xay duoc truoc markup</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OI MARKUP peak (19/07)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>26.56M USD (tu 4.47M T0: +22M trong 9 ngay)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MM_build_VWAP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.03943 USDT (daily 25/06-12/07 approx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MM_exit_VWAP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0.19710 USDT (1h klines 19-21/07, pos_r sap window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MM_multiple_thuc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5.00x (+400%) = exit_VWAP / build_VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MM_funding_PnL_PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$26K-$43K total (27/06-19/07, 3-5M long, khong dang ke)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gLSR_min_POST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.390 — 20/07 (ngay sau pos_r crash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>gLSR_slope_flip_sustained</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>28/07 (sau spike 27/07) — da tang lien tuc len 1.726 ngay 03/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pos_r_flat_window</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.30-1.36 (23-27/07) — khi px tang 0.247→0.376 (+42.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pos_r_crash_window</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>19-20/07: 1.61→1.09 (MM phan phoi trong khi px van tang)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>_probe_bank_h1h2h3_20260804.py run 04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3478,69 +3697,69 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="27" t="n">
         <v>0.0630603801681764</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="27">
         <f>IFERROR(B39/B38-1,"")</f>
         <v/>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="27" t="n">
         <v>562696137.64149</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="27" t="n">
         <v>0.491559894244458</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="27" t="n">
         <v>-0.001911111666666667</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="27" t="n">
         <v>-0.00438872</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="27" t="n">
         <v>-0.00069484</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="27" t="n">
         <v>17254036.24131712</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="27" t="n">
         <v>1.1095</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="27" t="n">
         <v>1.7933</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="27" t="n">
         <v>1.5013</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="27">
         <f>IFERROR(O39/P39,"")</f>
         <v/>
       </c>
-      <c r="S39">
+      <c r="S39" s="27">
         <f>IFERROR(AVERAGE(R37:R39),"")</f>
         <v/>
       </c>
-      <c r="T39">
+      <c r="T39" s="27">
         <f>IFERROR(Q39/Q34,"")</f>
         <v/>
       </c>
-      <c r="U39">
+      <c r="U39" s="27">
         <f>IFERROR(O39/O36-1,"")</f>
         <v/>
       </c>
-      <c r="V39">
+      <c r="V39" s="27">
         <f>IFERROR(P39/P36-1,"")</f>
         <v/>
       </c>
-      <c r="AJ39">
+      <c r="AJ39" s="27">
         <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
         <v/>
       </c>
@@ -3900,6 +4119,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="53" t="inlineStr">
         <is>
@@ -3958,12 +4178,30 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="33" t="n"/>
-      <c r="H4" s="33" t="n"/>
+      <c r="C4" s="33" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>+651.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>peak→down</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="n">
+        <v>51120000</v>
+      </c>
+      <c r="G4" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>px van cao (24/07 avg 0.283), OI 51M, gLSR 0.500 — POST dang sap</t>
+        </is>
+      </c>
       <c r="I4" s="33" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="28">

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -195,7 +195,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -357,6 +357,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,204 +759,204 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>px_T0 probe-verified</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>0.03773 (freshwatch 10/07 px_avg)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>px_max [1h spike native]</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>0.67205 USDT — 27/07 06:00 UTC (fapi 1h high, vol 299M USDT)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>px_max [daily avg basis]</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>0.37632 USDT — 26/07 freshwatch avg (truoc da dung lam px_max)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>px_max [close basis]</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>0.41958 USDT — 27/07 close (fapi 1h)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>markup T0→spike_high</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>+1681% (0.03773→0.67205)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>markup T0→daily_avg_max</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>+897% (0.03773→0.37632)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>OI PRE range (25/06-09/07)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>4.31M→4.73M FLAT — khong xay duoc truoc markup</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>OI MARKUP peak (19/07)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>26.56M USD (tu 4.47M T0: +22M trong 9 ngay)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>MM_build_VWAP</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>0.03943 USDT (daily 25/06-12/07 approx)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>MM_exit_VWAP</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>0.19710 USDT (1h klines 19-21/07, pos_r sap window)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>MM_multiple_thuc</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>5.00x (+400%) = exit_VWAP / build_VWAP</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>MM_funding_PnL_PRE_MARKUP</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>$26K-$43K total (27/06-19/07, 3-5M long, khong dang ke)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>gLSR_min_POST</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>0.390 — 20/07 (ngay sau pos_r crash)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>gLSR_slope_flip_sustained</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>28/07 (sau spike 27/07) — da tang lien tuc len 1.726 ngay 03/08)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>pos_r_flat_window</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>1.30-1.36 (23-27/07) — khi px tang 0.247→0.376 (+42.7%)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>pos_r_crash_window</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>19-20/07: 1.61→1.09 (MM phan phoi trong khi px van tang)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>_probe_bank_h1h2h3_20260804.py run 04/08/2026</t>
         </is>
@@ -3783,7 +3784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="27" min="1" max="1"/>
@@ -3972,6 +3973,94 @@
       <c r="D10" s="32" t="inlineStr">
         <is>
           <t>phan phoi hau-dinh, suppressor dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>06-05/06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mini-pump: vol 10M→25M→50.9M→41M (05-08/06), high 0.045, funding BURST 08/06 (23.4bps peak). Flush down 05/06 (low 0.022), recover 06-08/06. T-10 so với 17/06 unlock.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fapi klines + fundingRate (probe 04/08)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>bait-probe trước unlock Jun? (vol+funding chỉ dấu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unlock ~2% supply 17/06: QUIET (vol 1.6M, px ~0.04). Funding toàn PIN. Sau unlock: px -8% đến 22/06. acc_r=0.952 ngày 13/06 (ĐÃ CAO TRƯỚC UNLOCK).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fapi klines + freshwatch 09/06+13/06 (probe 04/08)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>unlock không kèm markup — đè sau để gom rẻ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07-17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unlock ~2% supply 17/07: TRONG đỉnh markup. px=0.068 (T+7). MM XẢ T+2→T+4 (19-21/07): pos_r 3.7→1.09, vol 1.4-6.5B/ngày. Khuôn L-12: kéo-trước-xả-vào-hype sau unlock.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>freshwatch + calib (probe 04/08)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>unlock = mốc xả MM; vol unlock = thanh khoản thoát</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07-27 06:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>px_max SPIKE 0.67205 USDT (1h native fapi). vol 299.72M USDT trong 1 nến. Close 0.419. Freshwatch daily avg 27/07=0.374. Wick spike — không phải close-based peak. px_max trước ghi 0.376 = WRONG.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fapi 1h klines (probe H1 04/08)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px_max thực = 0.672 spike, không phải 0.376 daily avg</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="27" min="1" max="1"/>
@@ -4188,7 +4277,7 @@
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>peak→down</t>
+          <t>spike_high=0.672 ngày 27/07 (wick); close_max=0.419; daily_avg_max=0.376 (26/07)</t>
         </is>
       </c>
       <c r="F4" s="33" t="n">
@@ -4241,6 +4330,18 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="33" t="n"/>
       <c r="I6" s="33" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>px_max SỬA (probe H1 04/08): 1h spike high = 0.67205 (27/07 06:00 UTC, 299M USDT). Daily avg max = 0.37632 (26/07 freshwatch). Close max = 0.41958 (27/07). Markup từ T0 (0.03773): +1681% spike / +897% daily avg / +1012% close.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4390,7 +4491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="27" min="1" max="1"/>
@@ -4404,6 +4505,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="31" t="inlineStr">
         <is>
@@ -4412,7 +4514,7 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PENDING (operator feed)</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4526,7 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>PENDING (CryptoRank/TokenUnlocks)</t>
+          <t>operator 04/08/2026 — CryptoRank/TokenUnlocks</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4538,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>17/08/2026 (T+38 từ T0 10/07) — ~2% supply/tháng</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4550,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>17/08 · 17/09 · 17/10 (~2%/tháng mỗi lần)</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4562,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>17/07/2026 — KHỚP exact với exit window 19-21/07 (T+7→T+9)</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4574,49 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>PENDING — viec tay #3 tracker</t>
+          <t>Khuôn L-12: MM xả T+2→T+4 sau unlock 17/07. Cảnh báo 17/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55">
+        <f>== UNLOCK CALENDAR (operator 04/08) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[PAST] Quanh 17/06: KHÔNG có markup. Trước đó 05-08/06 vol spike 50M→41M (mini-pump T-10 đến T-9). Funding BURST 08/06 (23.4bps). Unlock chính ngày 17/06 = QUIET (vol 1.6M). Sau 17/06: px giảm -8% đến 22/06. Pattern = đè-sau-unlock (chưa campaign).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[PAST — KHỚP CAMPAIGN] Unlock T+7 từ T0 (10/07). Trong đỉnh markup (+280% đến ngày này). MM XẢ T+2→T+4 sau unlock: pos_r 3.7→1.09 (19-21/07). KẾT LUẬN: unlock là mốc xả — MM dùng vol unlock làm thanh khoản thoát.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[UPCOMING — T+38 từ T0] CẢNH BÁO: token đang SUPPRESSED (px 0.043 = -93.6% từ spike 0.672). Nếu khuôn lặp: cửa sổ bait = 02/08→17/08. NHƯNG: pos_r chưa reset, không có bằng chứng MM build mới. → Theo dõi như RỦI RO (không phải cơ hội). Operator quyết.</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -195,7 +195,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -358,6 +358,8 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1714,6 +1716,17 @@
         <f>IFERROR(P9/P6-1,"")</f>
         <v/>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB9" s="56" t="n">
+        <v>286000</v>
+      </c>
+      <c r="AC9" s="57" t="n">
+        <v>0.67</v>
+      </c>
       <c r="AJ9" s="27">
         <f>IF(OR(AB9="",D9="",D9=0),"",AB9/D9)</f>
         <v/>
@@ -1782,6 +1795,17 @@
         <f>IFERROR(P10/P7-1,"")</f>
         <v/>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB10" s="56" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="AC10" s="57" t="n">
+        <v>0.512</v>
+      </c>
       <c r="AJ10" s="27">
         <f>IF(OR(AB10="",D10="",D10=0),"",AB10/D10)</f>
         <v/>
@@ -1850,6 +1874,17 @@
         <f>IFERROR(P11/P8-1,"")</f>
         <v/>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB11" s="56" t="n">
+        <v>397000</v>
+      </c>
+      <c r="AC11" s="57" t="n">
+        <v>0.363</v>
+      </c>
       <c r="AJ11" s="27">
         <f>IF(OR(AB11="",D11="",D11=0),"",AB11/D11)</f>
         <v/>
@@ -1918,6 +1953,17 @@
         <f>IFERROR(P12/P9-1,"")</f>
         <v/>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB12" s="56" t="n">
+        <v>203000</v>
+      </c>
+      <c r="AC12" s="57" t="n">
+        <v>0.376</v>
+      </c>
       <c r="AJ12" s="27">
         <f>IF(OR(AB12="",D12="",D12=0),"",AB12/D12)</f>
         <v/>
@@ -1986,6 +2032,17 @@
         <f>IFERROR(P13/P10-1,"")</f>
         <v/>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB13" s="56" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AC13" s="57" t="n">
+        <v>0.527</v>
+      </c>
       <c r="AJ13" s="27">
         <f>IF(OR(AB13="",D13="",D13=0),"",AB13/D13)</f>
         <v/>
@@ -2054,6 +2111,17 @@
         <f>IFERROR(P14/P11-1,"")</f>
         <v/>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB14" s="56" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC14" s="57" t="n">
+        <v>0.507</v>
+      </c>
       <c r="AJ14" s="27">
         <f>IF(OR(AB14="",D14="",D14=0),"",AB14/D14)</f>
         <v/>
@@ -2122,6 +2190,17 @@
         <f>IFERROR(P15/P12-1,"")</f>
         <v/>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB15" s="56" t="n">
+        <v>491000</v>
+      </c>
+      <c r="AC15" s="57" t="n">
+        <v>0.455</v>
+      </c>
       <c r="AJ15" s="27">
         <f>IF(OR(AB15="",D15="",D15=0),"",AB15/D15)</f>
         <v/>
@@ -2190,6 +2269,17 @@
         <f>IFERROR(P16/P13-1,"")</f>
         <v/>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB16" s="56" t="n">
+        <v>530000</v>
+      </c>
+      <c r="AC16" s="57" t="n">
+        <v>0.543</v>
+      </c>
       <c r="AJ16" s="27">
         <f>IF(OR(AB16="",D16="",D16=0),"",AB16/D16)</f>
         <v/>
@@ -2258,6 +2348,17 @@
         <f>IFERROR(P17/P14-1,"")</f>
         <v/>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB17" s="56" t="n">
+        <v>131000</v>
+      </c>
+      <c r="AC17" s="57" t="n">
+        <v>0.426</v>
+      </c>
       <c r="AJ17" s="27">
         <f>IF(OR(AB17="",D17="",D17=0),"",AB17/D17)</f>
         <v/>
@@ -2326,6 +2427,17 @@
         <f>IFERROR(P18/P15-1,"")</f>
         <v/>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB18" s="56" t="n">
+        <v>675000</v>
+      </c>
+      <c r="AC18" s="57" t="n">
+        <v>0.433</v>
+      </c>
       <c r="AJ18" s="27">
         <f>IF(OR(AB18="",D18="",D18=0),"",AB18/D18)</f>
         <v/>
@@ -2394,6 +2506,17 @@
         <f>IFERROR(P19/P16-1,"")</f>
         <v/>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB19" s="56" t="n">
+        <v>2440000</v>
+      </c>
+      <c r="AC19" s="57" t="n">
+        <v>0.477</v>
+      </c>
       <c r="AJ19" s="27">
         <f>IF(OR(AB19="",D19="",D19=0),"",AB19/D19)</f>
         <v/>
@@ -2462,6 +2585,17 @@
         <f>IFERROR(P20/P17-1,"")</f>
         <v/>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB20" s="56" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="AC20" s="57" t="n">
+        <v>0.437</v>
+      </c>
       <c r="AJ20" s="27">
         <f>IF(OR(AB20="",D20="",D20=0),"",AB20/D20)</f>
         <v/>
@@ -2530,6 +2664,17 @@
         <f>IFERROR(P21/P18-1,"")</f>
         <v/>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB21" s="56" t="n">
+        <v>573000</v>
+      </c>
+      <c r="AC21" s="57" t="n">
+        <v>0.491</v>
+      </c>
       <c r="AJ21" s="27">
         <f>IF(OR(AB21="",D21="",D21=0),"",AB21/D21)</f>
         <v/>
@@ -2598,6 +2743,17 @@
         <f>IFERROR(P22/P19-1,"")</f>
         <v/>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB22" s="56" t="n">
+        <v>459000</v>
+      </c>
+      <c r="AC22" s="57" t="n">
+        <v>0.605</v>
+      </c>
       <c r="AJ22" s="27">
         <f>IF(OR(AB22="",D22="",D22=0),"",AB22/D22)</f>
         <v/>
@@ -2666,6 +2822,17 @@
         <f>IFERROR(P23/P20-1,"")</f>
         <v/>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB23" s="56" t="n">
+        <v>2460000</v>
+      </c>
+      <c r="AC23" s="57" t="n">
+        <v>0.53</v>
+      </c>
       <c r="AJ23" s="27">
         <f>IF(OR(AB23="",D23="",D23=0),"",AB23/D23)</f>
         <v/>
@@ -2734,6 +2901,17 @@
         <f>IFERROR(P24/P21-1,"")</f>
         <v/>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB24" s="56" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="AC24" s="57" t="n">
+        <v>0.518</v>
+      </c>
       <c r="AJ24" s="27">
         <f>IF(OR(AB24="",D24="",D24=0),"",AB24/D24)</f>
         <v/>
@@ -2802,6 +2980,17 @@
         <f>IFERROR(P25/P22-1,"")</f>
         <v/>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB25" s="56" t="n">
+        <v>21450000</v>
+      </c>
+      <c r="AC25" s="57" t="n">
+        <v>0.497</v>
+      </c>
       <c r="AJ25" s="27">
         <f>IF(OR(AB25="",D25="",D25=0),"",AB25/D25)</f>
         <v/>
@@ -2870,6 +3059,17 @@
         <f>IFERROR(P26/P23-1,"")</f>
         <v/>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB26" s="56" t="n">
+        <v>29800000</v>
+      </c>
+      <c r="AC26" s="57" t="n">
+        <v>0.528</v>
+      </c>
       <c r="AJ26" s="27">
         <f>IF(OR(AB26="",D26="",D26=0),"",AB26/D26)</f>
         <v/>
@@ -2938,6 +3138,17 @@
         <f>IFERROR(P27/P24-1,"")</f>
         <v/>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB27" s="56" t="n">
+        <v>114270000</v>
+      </c>
+      <c r="AC27" s="57" t="n">
+        <v>0.522</v>
+      </c>
       <c r="AJ27" s="27">
         <f>IF(OR(AB27="",D27="",D27=0),"",AB27/D27)</f>
         <v/>
@@ -3006,6 +3217,17 @@
         <f>IFERROR(P28/P25-1,"")</f>
         <v/>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB28" s="56" t="n">
+        <v>77060000</v>
+      </c>
+      <c r="AC28" s="57" t="n">
+        <v>0.528</v>
+      </c>
       <c r="AJ28" s="27">
         <f>IF(OR(AB28="",D28="",D28=0),"",AB28/D28)</f>
         <v/>
@@ -3074,6 +3296,17 @@
         <f>IFERROR(P29/P26-1,"")</f>
         <v/>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB29" s="56" t="n">
+        <v>97030000</v>
+      </c>
+      <c r="AC29" s="57" t="n">
+        <v>0.499</v>
+      </c>
       <c r="AJ29" s="27">
         <f>IF(OR(AB29="",D29="",D29=0),"",AB29/D29)</f>
         <v/>
@@ -3142,6 +3375,17 @@
         <f>IFERROR(P30/P27-1,"")</f>
         <v/>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB30" s="56" t="n">
+        <v>97100000</v>
+      </c>
+      <c r="AC30" s="57" t="n">
+        <v>0.509</v>
+      </c>
       <c r="AJ30" s="27">
         <f>IF(OR(AB30="",D30="",D30=0),"",AB30/D30)</f>
         <v/>
@@ -3210,6 +3454,17 @@
         <f>IFERROR(P31/P28-1,"")</f>
         <v/>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB31" s="56" t="n">
+        <v>55960000</v>
+      </c>
+      <c r="AC31" s="57" t="n">
+        <v>0.505</v>
+      </c>
       <c r="AJ31" s="27">
         <f>IF(OR(AB31="",D31="",D31=0),"",AB31/D31)</f>
         <v/>
@@ -3278,6 +3533,17 @@
         <f>IFERROR(P32/P29-1,"")</f>
         <v/>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB32" s="56" t="n">
+        <v>65500000</v>
+      </c>
+      <c r="AC32" s="57" t="n">
+        <v>0.507</v>
+      </c>
       <c r="AJ32" s="27">
         <f>IF(OR(AB32="",D32="",D32=0),"",AB32/D32)</f>
         <v/>
@@ -3346,6 +3612,17 @@
         <f>IFERROR(P33/P30-1,"")</f>
         <v/>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB33" s="56" t="n">
+        <v>45180000</v>
+      </c>
+      <c r="AC33" s="57" t="n">
+        <v>0.511</v>
+      </c>
       <c r="AJ33" s="27">
         <f>IF(OR(AB33="",D33="",D33=0),"",AB33/D33)</f>
         <v/>
@@ -3419,6 +3696,17 @@
           <t>lsr_accum|stealth_grind|oi_ignition</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB34" s="56" t="n">
+        <v>35560000</v>
+      </c>
+      <c r="AC34" s="57" t="n">
+        <v>0.514</v>
+      </c>
       <c r="AJ34" s="27">
         <f>IF(OR(AB34="",D34="",D34=0),"",AB34/D34)</f>
         <v/>
@@ -3497,6 +3785,17 @@
           <t>lsr_accum|stealth_grind|oi_ignition</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB35" s="56" t="n">
+        <v>124750000</v>
+      </c>
+      <c r="AC35" s="57" t="n">
+        <v>0.517</v>
+      </c>
       <c r="AJ35" s="27">
         <f>IF(OR(AB35="",D35="",D35=0),"",AB35/D35)</f>
         <v/>
@@ -3551,6 +3850,17 @@
           <t>dist_wall|post_climax</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB36" s="56" t="n">
+        <v>116370000</v>
+      </c>
+      <c r="AC36" s="57" t="n">
+        <v>0.511</v>
+      </c>
       <c r="AJ36" s="27">
         <f>IF(OR(AB36="",D36="",D36=0),"",AB36/D36)</f>
         <v/>
@@ -3578,7 +3888,7 @@
         <v>738355605.75427</v>
       </c>
       <c r="E37" s="27" t="n">
-        <v>0.4989226837701057</v>
+        <v>49.892268</v>
       </c>
       <c r="F37" s="27" t="n">
         <v>-0.000988205</v>
@@ -3624,6 +3934,17 @@
         <f>IFERROR(P37/P34-1,"")</f>
         <v/>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB37" s="56" t="n">
+        <v>66910000</v>
+      </c>
+      <c r="AC37" s="57" t="n">
+        <v>0.507</v>
+      </c>
       <c r="AJ37" s="27">
         <f>IF(OR(AB37="",D37="",D37=0),"",AB37/D37)</f>
         <v/>
@@ -3646,7 +3967,7 @@
         <v>1039593900.21891</v>
       </c>
       <c r="E38" s="27" t="n">
-        <v>0.491663277755185</v>
+        <v>49.166328</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>-0.003337582</v>
@@ -3692,6 +4013,17 @@
         <f>IFERROR(P38/P35-1,"")</f>
         <v/>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB38" s="56" t="n">
+        <v>85580000</v>
+      </c>
+      <c r="AC38" s="57" t="n">
+        <v>0.465</v>
+      </c>
       <c r="AJ38" s="27">
         <f>IF(OR(AB38="",D38="",D38=0),"",AB38/D38)</f>
         <v/>
@@ -3714,7 +4046,7 @@
         <v>562696137.64149</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>0.491559894244458</v>
+        <v>49.155989</v>
       </c>
       <c r="F39" s="27" t="n">
         <v>-0.001911111666666667</v>
@@ -3759,6 +4091,17 @@
       <c r="V39" s="27">
         <f>IFERROR(P39/P36-1,"")</f>
         <v/>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB39" s="56" t="n">
+        <v>35330000</v>
+      </c>
+      <c r="AC39" s="57" t="n">
+        <v>0.466</v>
       </c>
       <c r="AJ39" s="27">
         <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
@@ -3977,88 +4320,88 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>06-05/06</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>mini-pump: vol 10M→25M→50.9M→41M (05-08/06), high 0.045, funding BURST 08/06 (23.4bps peak). Flush down 05/06 (low 0.022), recover 06-08/06. T-10 so với 17/06 unlock.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>fapi klines + fundingRate (probe 04/08)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>bait-probe trước unlock Jun? (vol+funding chỉ dấu)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>06-17</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Unlock ~2% supply 17/06: QUIET (vol 1.6M, px ~0.04). Funding toàn PIN. Sau unlock: px -8% đến 22/06. acc_r=0.952 ngày 13/06 (ĐÃ CAO TRƯỚC UNLOCK).</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>fapi klines + freshwatch 09/06+13/06 (probe 04/08)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>unlock không kèm markup — đè sau để gom rẻ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>07-17</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Unlock ~2% supply 17/07: TRONG đỉnh markup. px=0.068 (T+7). MM XẢ T+2→T+4 (19-21/07): pos_r 3.7→1.09, vol 1.4-6.5B/ngày. Khuôn L-12: kéo-trước-xả-vào-hype sau unlock.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>freshwatch + calib (probe 04/08)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>unlock = mốc xả MM; vol unlock = thanh khoản thoát</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>07-27 06:00</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>px_max SPIKE 0.67205 USDT (1h native fapi). vol 299.72M USDT trong 1 nến. Close 0.419. Freshwatch daily avg 27/07=0.374. Wick spike — không phải close-based peak. px_max trước ghi 0.376 = WRONG.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>fapi 1h klines (probe H1 04/08)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>px_max thực = 0.672 spike, không phải 0.376 daily avg</t>
         </is>
@@ -4208,7 +4551,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="53" t="inlineStr">
         <is>
@@ -4332,12 +4674,12 @@
       <c r="I6" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>px_max SỬA (probe H1 04/08): 1h spike high = 0.67205 (27/07 06:00 UTC, 299M USDT). Daily avg max = 0.37632 (26/07 freshwatch). Close max = 0.41958 (27/07). Markup từ T0 (0.03773): +1681% spike / +897% daily avg / +1012% close.</t>
         </is>
@@ -4505,7 +4847,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="31" t="inlineStr">
         <is>
@@ -4585,36 +4926,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>[PAST] Quanh 17/06: KHÔNG có markup. Trước đó 05-08/06 vol spike 50M→41M (mini-pump T-10 đến T-9). Funding BURST 08/06 (23.4bps). Unlock chính ngày 17/06 = QUIET (vol 1.6M). Sau 17/06: px giảm -8% đến 22/06. Pattern = đè-sau-unlock (chưa campaign).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>[PAST — KHỚP CAMPAIGN] Unlock T+7 từ T0 (10/07). Trong đỉnh markup (+280% đến ngày này). MM XẢ T+2→T+4 sau unlock: pos_r 3.7→1.09 (19-21/07). KẾT LUẬN: unlock là mốc xả — MM dùng vol unlock làm thanh khoản thoát.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>[UPCOMING — T+38 từ T0] CẢNH BÁO: token đang SUPPRESSED (px 0.043 = -93.6% từ spike 0.672). Nếu khuôn lặp: cửa sổ bait = 02/08→17/08. NHƯNG: pos_r chưa reset, không có bằng chứng MM build mới. → Theo dõi như RỦI RO (không phải cơ hội). Operator quyết.</t>
         </is>

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -30,6 +30,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0.00000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -100,7 +101,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -160,6 +161,11 @@
         <fgColor rgb="00D4A843"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -195,7 +201,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -360,6 +366,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -977,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AO39"/>
+  <dimension ref="A1:AO44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="27" min="1" max="1"/>
@@ -1716,7 +1732,7 @@
         <f>IFERROR(P9/P6-1,"")</f>
         <v/>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA9" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -1795,7 +1811,7 @@
         <f>IFERROR(P10/P7-1,"")</f>
         <v/>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA10" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -1874,7 +1890,7 @@
         <f>IFERROR(P11/P8-1,"")</f>
         <v/>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA11" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -1953,7 +1969,7 @@
         <f>IFERROR(P12/P9-1,"")</f>
         <v/>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA12" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2032,7 +2048,7 @@
         <f>IFERROR(P13/P10-1,"")</f>
         <v/>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA13" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2111,7 +2127,7 @@
         <f>IFERROR(P14/P11-1,"")</f>
         <v/>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA14" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2190,7 +2206,7 @@
         <f>IFERROR(P15/P12-1,"")</f>
         <v/>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA15" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2269,7 +2285,7 @@
         <f>IFERROR(P16/P13-1,"")</f>
         <v/>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA16" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2348,7 +2364,7 @@
         <f>IFERROR(P17/P14-1,"")</f>
         <v/>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA17" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2427,7 +2443,7 @@
         <f>IFERROR(P18/P15-1,"")</f>
         <v/>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA18" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2506,7 +2522,7 @@
         <f>IFERROR(P19/P16-1,"")</f>
         <v/>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA19" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2585,7 +2601,7 @@
         <f>IFERROR(P20/P17-1,"")</f>
         <v/>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA20" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2664,7 +2680,7 @@
         <f>IFERROR(P21/P18-1,"")</f>
         <v/>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA21" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2743,7 +2759,7 @@
         <f>IFERROR(P22/P19-1,"")</f>
         <v/>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA22" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2822,7 +2838,7 @@
         <f>IFERROR(P23/P20-1,"")</f>
         <v/>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA23" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2901,7 +2917,7 @@
         <f>IFERROR(P24/P21-1,"")</f>
         <v/>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA24" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -2980,7 +2996,7 @@
         <f>IFERROR(P25/P22-1,"")</f>
         <v/>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA25" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3059,7 +3075,7 @@
         <f>IFERROR(P26/P23-1,"")</f>
         <v/>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA26" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3138,7 +3154,7 @@
         <f>IFERROR(P27/P24-1,"")</f>
         <v/>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA27" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3217,7 +3233,7 @@
         <f>IFERROR(P28/P25-1,"")</f>
         <v/>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA28" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3296,7 +3312,7 @@
         <f>IFERROR(P29/P26-1,"")</f>
         <v/>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA29" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3375,7 +3391,7 @@
         <f>IFERROR(P30/P27-1,"")</f>
         <v/>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA30" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3454,7 +3470,7 @@
         <f>IFERROR(P31/P28-1,"")</f>
         <v/>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA31" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3533,7 +3549,7 @@
         <f>IFERROR(P32/P29-1,"")</f>
         <v/>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA32" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3612,7 +3628,7 @@
         <f>IFERROR(P33/P30-1,"")</f>
         <v/>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AA33" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3696,7 +3712,7 @@
           <t>lsr_accum|stealth_grind|oi_ignition</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AA34" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3785,7 +3801,7 @@
           <t>lsr_accum|stealth_grind|oi_ignition</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AA35" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3850,7 +3866,7 @@
           <t>dist_wall|post_climax</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AA36" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -3934,7 +3950,7 @@
         <f>IFERROR(P37/P34-1,"")</f>
         <v/>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AA37" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -4013,7 +4029,7 @@
         <f>IFERROR(P38/P35-1,"")</f>
         <v/>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA38" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -4092,7 +4108,7 @@
         <f>IFERROR(P39/P36-1,"")</f>
         <v/>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AA39" s="27" t="inlineStr">
         <is>
           <t>Binance_spot</t>
         </is>
@@ -4107,6 +4123,345 @@
         <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
         <v/>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="n">
+        <v>0.056915</v>
+      </c>
+      <c r="C40" s="57" t="n">
+        <v>-0.09745231715678249</v>
+      </c>
+      <c r="D40" s="57" t="n">
+        <v>253304478</v>
+      </c>
+      <c r="E40" s="57" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.000806</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.002363</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.000139</v>
+      </c>
+      <c r="I40" t="n">
+        <v>24</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>neg_batch</t>
+        </is>
+      </c>
+      <c r="K40" s="56" t="n"/>
+      <c r="L40" t="n">
+        <v>18027284</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.1805</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.0276</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.7996</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.5822154271059381</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="56" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB40" s="57" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.462</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="58" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B41" s="59" t="n">
+        <v>0.047883</v>
+      </c>
+      <c r="C41" s="57" t="n">
+        <v>-0.1586927874901168</v>
+      </c>
+      <c r="D41" s="57" t="n">
+        <v>172554826</v>
+      </c>
+      <c r="E41" s="57" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.000349</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.000722</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-9.66e-05</v>
+      </c>
+      <c r="I41" t="n">
+        <v>24</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>neg_light</t>
+        </is>
+      </c>
+      <c r="K41" s="56" t="n"/>
+      <c r="L41" t="n">
+        <v>17469390</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.3197</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.2658</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.8843</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.5824432871392003</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="56" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB41" s="57" t="n">
+        <v>12180000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.493</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="58" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B42" s="59" t="n">
+        <v>0.043163</v>
+      </c>
+      <c r="C42" s="57" t="n">
+        <v>-0.09857360649917513</v>
+      </c>
+      <c r="D42" s="57" t="n">
+        <v>143022585</v>
+      </c>
+      <c r="E42" s="57" t="n">
+        <v>0.4883</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.000186</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.000821</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.5e-06</v>
+      </c>
+      <c r="I42" t="n">
+        <v>24</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>neg_light</t>
+        </is>
+      </c>
+      <c r="K42" s="56" t="n"/>
+      <c r="L42" t="n">
+        <v>17252550</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.3123</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.1466</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.7263</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.6113388614553248</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="56" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB42" s="57" t="n">
+        <v>12350000</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.481</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="58" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B43" s="59" t="n">
+        <v>0.051353</v>
+      </c>
+      <c r="C43" s="57" t="n">
+        <v>0.1897458471375948</v>
+      </c>
+      <c r="D43" s="57" t="n">
+        <v>471564742</v>
+      </c>
+      <c r="E43" s="57" t="n">
+        <v>0.4906</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.000548</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.002347</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="I43" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>neg_batch</t>
+        </is>
+      </c>
+      <c r="K43" s="56" t="n"/>
+      <c r="L43" t="n">
+        <v>17356910</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.3135</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6419843597262952</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="56" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB43" s="57" t="n">
+        <v>46830000</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.483</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="C44" s="62" t="n">
+        <v>0.01065176328549455</v>
+      </c>
+      <c r="D44" s="62" t="n">
+        <v>102200000</v>
+      </c>
+      <c r="E44" s="62" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="F44" s="63" t="n"/>
+      <c r="G44" s="63" t="n"/>
+      <c r="H44" s="63" t="n"/>
+      <c r="I44" s="63" t="n"/>
+      <c r="J44" s="63" t="inlineStr">
+        <is>
+          <t>near_zero</t>
+        </is>
+      </c>
+      <c r="K44" s="64" t="n"/>
+      <c r="L44" s="63" t="n">
+        <v>18070000</v>
+      </c>
+      <c r="M44" s="63" t="n"/>
+      <c r="N44" s="63" t="n"/>
+      <c r="O44" s="63" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="P44" s="63" t="n"/>
+      <c r="Q44" s="63" t="n">
+        <v>1.396</v>
+      </c>
+      <c r="R44" s="63" t="n"/>
+      <c r="S44" s="63" t="n"/>
+      <c r="T44" s="63" t="n"/>
+      <c r="U44" s="63" t="n"/>
+      <c r="V44" s="63" t="n"/>
+      <c r="W44" s="63" t="n"/>
+      <c r="X44" s="63" t="n"/>
+      <c r="Y44" s="63" t="n"/>
+      <c r="Z44" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="64" t="inlineStr">
+        <is>
+          <t>Binance_spot</t>
+        </is>
+      </c>
+      <c r="AB44" s="62" t="n">
+        <v>6860000</v>
+      </c>
+      <c r="AC44" s="63" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="AD44" s="63" t="n"/>
+      <c r="AE44" s="63" t="n"/>
+      <c r="AF44" s="63" t="n"/>
+      <c r="AG44" s="63" t="n"/>
+      <c r="AH44" s="63" t="n"/>
+      <c r="AI44" s="63" t="n"/>
+      <c r="AJ44" s="63" t="n"/>
+      <c r="AK44" s="63" t="n"/>
+      <c r="AL44" s="63" t="n"/>
+      <c r="AM44" s="63" t="n"/>
+      <c r="AN44" s="63" t="n"/>
+      <c r="AO44" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4551,6 +4906,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="53" t="inlineStr">
         <is>
@@ -4646,13 +5002,27 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
+      <c r="C5" s="65" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>+31.3% vs T0=0.0377</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>Tu +897% dinh (0.672, 27/07 wick) ve +31.3%. advisor exit VWAP 0.1971 -&gt; px_now/exit = -74.9%. Crowd giu tui -73.4% tu exit.</t>
+        </is>
+      </c>
       <c r="F5" s="33" t="n"/>
       <c r="G5" s="33" t="n"/>
       <c r="H5" s="33" t="n"/>
-      <c r="I5" s="33" t="n"/>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>MUA_T0_DUNG — exit advisor 19-21/07 chuan xac</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="28">
       <c r="A6" s="32" t="inlineStr">

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -993,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AO44"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="27" min="1" max="1"/>
@@ -4142,40 +4142,40 @@
       <c r="E40" s="57" t="n">
         <v>0.4804</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="27" t="n">
         <v>-0.000806</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="27" t="n">
         <v>-0.002363</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="27" t="n">
         <v>-0.000139</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="27" t="inlineStr">
         <is>
           <t>neg_batch</t>
         </is>
       </c>
       <c r="K40" s="56" t="n"/>
-      <c r="L40" t="n">
+      <c r="L40" s="27" t="n">
         <v>18027284</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="27" t="n">
         <v>1.1805</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40" s="27" t="n">
         <v>2.0276</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" s="27" t="n">
         <v>1.7996</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R40" s="27" t="n">
         <v>0.5822154271059381</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="Z40" s="27" t="n">
         <v>0</v>
       </c>
       <c r="AA40" s="56" t="inlineStr">
@@ -4186,7 +4186,7 @@
       <c r="AB40" s="57" t="n">
         <v>19910000</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AC40" s="27" t="n">
         <v>0.462</v>
       </c>
     </row>
@@ -4208,40 +4208,40 @@
       <c r="E41" s="57" t="n">
         <v>0.4791</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="27" t="n">
         <v>-0.000349</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="27" t="n">
         <v>-0.000722</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="27" t="n">
         <v>-9.66e-05</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="27" t="inlineStr">
         <is>
           <t>neg_light</t>
         </is>
       </c>
       <c r="K41" s="56" t="n"/>
-      <c r="L41" t="n">
+      <c r="L41" s="27" t="n">
         <v>17469390</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="27" t="n">
         <v>1.3197</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41" s="27" t="n">
         <v>2.2658</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="27" t="n">
         <v>1.8843</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R41" s="27" t="n">
         <v>0.5824432871392003</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="Z41" s="27" t="n">
         <v>0</v>
       </c>
       <c r="AA41" s="56" t="inlineStr">
@@ -4252,7 +4252,7 @@
       <c r="AB41" s="57" t="n">
         <v>12180000</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AC41" s="27" t="n">
         <v>0.493</v>
       </c>
     </row>
@@ -4274,40 +4274,40 @@
       <c r="E42" s="57" t="n">
         <v>0.4883</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="27" t="n">
         <v>-0.000186</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="27" t="n">
         <v>-0.000821</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="27" t="n">
         <v>3.5e-06</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="27" t="inlineStr">
         <is>
           <t>neg_light</t>
         </is>
       </c>
       <c r="K42" s="56" t="n"/>
-      <c r="L42" t="n">
+      <c r="L42" s="27" t="n">
         <v>17252550</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" s="27" t="n">
         <v>1.3123</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42" s="27" t="n">
         <v>2.1466</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="27" t="n">
         <v>1.7263</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R42" s="27" t="n">
         <v>0.6113388614553248</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="Z42" s="27" t="n">
         <v>0</v>
       </c>
       <c r="AA42" s="56" t="inlineStr">
@@ -4318,7 +4318,7 @@
       <c r="AB42" s="57" t="n">
         <v>12350000</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AC42" s="27" t="n">
         <v>0.481</v>
       </c>
     </row>
@@ -4340,40 +4340,40 @@
       <c r="E43" s="57" t="n">
         <v>0.4906</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="27" t="n">
         <v>-0.000548</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="27" t="n">
         <v>-0.002347</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="27" t="n">
         <v>1.25e-05</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="27" t="inlineStr">
         <is>
           <t>neg_batch</t>
         </is>
       </c>
       <c r="K43" s="56" t="n"/>
-      <c r="L43" t="n">
+      <c r="L43" s="27" t="n">
         <v>17356910</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" s="27" t="n">
         <v>1.3135</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43" s="27" t="n">
         <v>2.046</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" s="27" t="n">
         <v>1.649</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R43" s="27" t="n">
         <v>0.6419843597262952</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="Z43" s="27" t="n">
         <v>0</v>
       </c>
       <c r="AA43" s="56" t="inlineStr">
@@ -4384,7 +4384,7 @@
       <c r="AB43" s="57" t="n">
         <v>46830000</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AC43" s="27" t="n">
         <v>0.483</v>
       </c>
     </row>
@@ -4462,6 +4462,482 @@
       <c r="AM44" s="63" t="n"/>
       <c r="AN44" s="63" t="n"/>
       <c r="AO44" s="63" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="n">
+        <v>0.0404143452896341</v>
+      </c>
+      <c r="C45" s="27">
+        <f>IFERROR(B45/B44-1,"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>140686649.01256</v>
+      </c>
+      <c r="E45" s="27" t="n">
+        <v>47.657681</v>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>4.8475e-05</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>4.416e-05</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" s="27" t="n">
+        <v>12984678.97891008</v>
+      </c>
+      <c r="O45" s="27" t="n">
+        <v>1.5928</v>
+      </c>
+      <c r="P45" s="27" t="n">
+        <v>1.8433</v>
+      </c>
+      <c r="Q45" s="27" t="n">
+        <v>1.4295</v>
+      </c>
+      <c r="R45" s="27">
+        <f>IFERROR(O45/P45,"")</f>
+        <v/>
+      </c>
+      <c r="S45" s="27">
+        <f>IFERROR(AVERAGE(R43:R45),"")</f>
+        <v/>
+      </c>
+      <c r="T45" s="27">
+        <f>IFERROR(Q45/Q40,"")</f>
+        <v/>
+      </c>
+      <c r="U45" s="27">
+        <f>IFERROR(O45/O42-1,"")</f>
+        <v/>
+      </c>
+      <c r="V45" s="27">
+        <f>IFERROR(P45/P42-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ45" s="27">
+        <f>IF(OR(AB45="",D45="",D45=0),"",AB45/D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>0.0389331582839826</v>
+      </c>
+      <c r="C46" s="27">
+        <f>IFERROR(B46/B45-1,"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="27" t="n">
+        <v>42263053.84667</v>
+      </c>
+      <c r="E46" s="27" t="n">
+        <v>49.246308</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>-9.721166666666668e-05</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>-0.00029585</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L46" s="27" t="n">
+        <v>13196123.73636998</v>
+      </c>
+      <c r="O46" s="27" t="n">
+        <v>1.4526</v>
+      </c>
+      <c r="P46" s="27" t="n">
+        <v>1.9412</v>
+      </c>
+      <c r="Q46" s="27" t="n">
+        <v>1.4498</v>
+      </c>
+      <c r="R46" s="27">
+        <f>IFERROR(O46/P46,"")</f>
+        <v/>
+      </c>
+      <c r="S46" s="27">
+        <f>IFERROR(AVERAGE(R44:R46),"")</f>
+        <v/>
+      </c>
+      <c r="T46" s="27">
+        <f>IFERROR(Q46/Q41,"")</f>
+        <v/>
+      </c>
+      <c r="U46" s="27">
+        <f>IFERROR(O46/O43-1,"")</f>
+        <v/>
+      </c>
+      <c r="V46" s="27">
+        <f>IFERROR(P46/P43-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ46" s="27">
+        <f>IF(OR(AB46="",D46="",D46=0),"",AB46/D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n">
+        <v>0.0373057526039732</v>
+      </c>
+      <c r="C47" s="27">
+        <f>IFERROR(B47/B46-1,"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="27" t="n">
+        <v>45394765.99188</v>
+      </c>
+      <c r="E47" s="27" t="n">
+        <v>46.007235</v>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>-8.702333333333332e-05</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>-0.00030814</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>3.123e-05</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" s="27" t="n">
+        <v>13337814.73104</v>
+      </c>
+      <c r="O47" s="27" t="n">
+        <v>1.5683</v>
+      </c>
+      <c r="P47" s="27" t="n">
+        <v>2.0469</v>
+      </c>
+      <c r="Q47" s="27" t="n">
+        <v>1.5813</v>
+      </c>
+      <c r="R47" s="27">
+        <f>IFERROR(O47/P47,"")</f>
+        <v/>
+      </c>
+      <c r="S47" s="27">
+        <f>IFERROR(AVERAGE(R45:R47),"")</f>
+        <v/>
+      </c>
+      <c r="T47" s="27">
+        <f>IFERROR(Q47/Q42,"")</f>
+        <v/>
+      </c>
+      <c r="U47" s="27">
+        <f>IFERROR(O47/O44-1,"")</f>
+        <v/>
+      </c>
+      <c r="V47" s="27">
+        <f>IFERROR(P47/P44-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ47" s="27">
+        <f>IF(OR(AB47="",D47="",D47=0),"",AB47/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="n">
+        <v>0.0363926583940916</v>
+      </c>
+      <c r="C48" s="27">
+        <f>IFERROR(B48/B47-1,"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="27" t="n">
+        <v>54495385.01868</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>48.408399</v>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>-0.000389125</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>-0.00084272</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>6.02e-06</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" s="27" t="n">
+        <v>11832075.85119</v>
+      </c>
+      <c r="O48" s="27" t="n">
+        <v>1.5795</v>
+      </c>
+      <c r="P48" s="27" t="n">
+        <v>1.907</v>
+      </c>
+      <c r="Q48" s="27" t="n">
+        <v>1.3883</v>
+      </c>
+      <c r="R48" s="27">
+        <f>IFERROR(O48/P48,"")</f>
+        <v/>
+      </c>
+      <c r="S48" s="27">
+        <f>IFERROR(AVERAGE(R46:R48),"")</f>
+        <v/>
+      </c>
+      <c r="T48" s="27">
+        <f>IFERROR(Q48/Q43,"")</f>
+        <v/>
+      </c>
+      <c r="U48" s="27">
+        <f>IFERROR(O48/O45-1,"")</f>
+        <v/>
+      </c>
+      <c r="V48" s="27">
+        <f>IFERROR(P48/P45-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ48" s="27">
+        <f>IF(OR(AB48="",D48="",D48=0),"",AB48/D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="n">
+        <v>0.0373570870676163</v>
+      </c>
+      <c r="C49" s="27">
+        <f>IFERROR(B49/B48-1,"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="27" t="n">
+        <v>43707076.14468</v>
+      </c>
+      <c r="E49" s="27" t="n">
+        <v>48.253558</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>1.937e-05</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>-7.900000000000001e-06</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L49" s="27" t="n">
+        <v>11813030.8373</v>
+      </c>
+      <c r="O49" s="27" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="P49" s="27" t="n">
+        <v>1.8662</v>
+      </c>
+      <c r="Q49" s="27" t="n">
+        <v>1.4462</v>
+      </c>
+      <c r="R49" s="27">
+        <f>IFERROR(O49/P49,"")</f>
+        <v/>
+      </c>
+      <c r="S49" s="27">
+        <f>IFERROR(AVERAGE(R47:R49),"")</f>
+        <v/>
+      </c>
+      <c r="T49" s="27">
+        <f>IFERROR(Q49/Q44,"")</f>
+        <v/>
+      </c>
+      <c r="U49" s="27">
+        <f>IFERROR(O49/O46-1,"")</f>
+        <v/>
+      </c>
+      <c r="V49" s="27">
+        <f>IFERROR(P49/P46-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ49" s="27">
+        <f>IF(OR(AB49="",D49="",D49=0),"",AB49/D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>0.0375901118292134</v>
+      </c>
+      <c r="C50" s="27">
+        <f>IFERROR(B50/B49-1,"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="27" t="n">
+        <v>28138687.39511</v>
+      </c>
+      <c r="E50" s="27" t="n">
+        <v>47.210051</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>4.253166666666667e-05</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>5.19e-06</v>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L50" s="27" t="n">
+        <v>11699705.86807</v>
+      </c>
+      <c r="O50" s="27" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="P50" s="27" t="n">
+        <v>1.7824</v>
+      </c>
+      <c r="Q50" s="27" t="n">
+        <v>1.3838</v>
+      </c>
+      <c r="R50" s="27">
+        <f>IFERROR(O50/P50,"")</f>
+        <v/>
+      </c>
+      <c r="S50" s="27">
+        <f>IFERROR(AVERAGE(R48:R50),"")</f>
+        <v/>
+      </c>
+      <c r="T50" s="27">
+        <f>IFERROR(Q50/Q45,"")</f>
+        <v/>
+      </c>
+      <c r="U50" s="27">
+        <f>IFERROR(O50/O47-1,"")</f>
+        <v/>
+      </c>
+      <c r="V50" s="27">
+        <f>IFERROR(P50/P47-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ50" s="27">
+        <f>IF(OR(AB50="",D50="",D50=0),"",AB50/D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.03635792928012117</v>
+      </c>
+      <c r="C51">
+        <f>IFERROR(B51/B50-1,"")</f>
+        <v/>
+      </c>
+      <c r="D51" t="n">
+        <v>19287848.72461</v>
+      </c>
+      <c r="E51" t="n">
+        <v>46.141003</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.4445e-05</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-4.002e-05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" t="n">
+        <v>11251300.09384519</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.6943</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.8466</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.4015</v>
+      </c>
+      <c r="R51">
+        <f>IFERROR(O51/P51,"")</f>
+        <v/>
+      </c>
+      <c r="S51">
+        <f>IFERROR(AVERAGE(R49:R51),"")</f>
+        <v/>
+      </c>
+      <c r="T51">
+        <f>IFERROR(Q51/Q46,"")</f>
+        <v/>
+      </c>
+      <c r="U51">
+        <f>IFERROR(O51/O48-1,"")</f>
+        <v/>
+      </c>
+      <c r="V51">
+        <f>IFERROR(P51/P48-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ51">
+        <f>IF(OR(AB51="",D51="",D51=0),"",AB51/D51)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4906,7 +5382,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="53" t="inlineStr">
         <is>

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="27" min="1" max="1"/>
@@ -977,6 +977,92 @@
       <c r="B33" s="27" t="inlineStr">
         <is>
           <t>_probe_bank_h1h2h3_20260804.py run 04/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE (R7 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>first_nn LSR (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>first_nn OI (fapi 30d)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>N/A-GAP dates (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-24, 2026-07-25, 2026-07-26, 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>N/A-RETENTION rule</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trước first_nn = N/A-RETENTION (store không cover, không collect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CORRECTIONS (R8 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gap 24-26/07 nguồn store</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3 ngày freshwatch drop toàn universe (họ TUT+BTW) — không sửa lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Schema-migration R4 v2.1 partial</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>cols 42-45 = o/h/l/c append (append-only per L-57 R4) · cols 46-47 = vol_alpha/taker_alpha CHƯA-TRA (chờ nhịp 2 R5) · cols 51-52 = vol_spot_ext_usd/spot_ext_venue CHƯA-TRA (chờ nhịp 2 R5) · cols 48-50 reserved. Cột v1 cũ (1-41) KHÔNG đè.</t>
         </is>
       </c>
     </row>
@@ -993,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AO51"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="27" min="1" max="1"/>
@@ -1047,6 +1133,36 @@
           <t>MANUAL (operator)</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>OHLC-append (R4)</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>vol_alpha-append (R4)</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>SPOT-EXT (v2.1 R4 21/08)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="40" t="inlineStr">
@@ -1254,6 +1370,49 @@
           <t>mm_note</t>
         </is>
       </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>vol_alpha</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>taker_alpha</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>spot_ext_venue</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="43" t="inlineStr">
@@ -1262,17 +1421,17 @@
         </is>
       </c>
       <c r="B3" s="44" t="n">
-        <v>0.041833546</v>
+        <v>0.03774</v>
       </c>
       <c r="C3" s="27">
         <f>IFERROR(B3/B2-1,"")</f>
         <v/>
       </c>
       <c r="D3" s="45" t="n">
-        <v>670000</v>
+        <v>13325534.84</v>
       </c>
       <c r="E3" s="46" t="n">
-        <v>0.5436</v>
+        <v>49.2302</v>
       </c>
       <c r="F3" s="47" t="n">
         <v>5e-05</v>
@@ -1284,7 +1443,7 @@
         <v>5e-05</v>
       </c>
       <c r="I3" s="48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" s="45" t="n">
         <v>5100000</v>
@@ -1325,6 +1484,38 @@
         <v/>
       </c>
       <c r="AN3" s="51" t="n"/>
+      <c r="AP3" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.04463</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.03658</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.03774</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="28">
       <c r="A4" s="43" t="inlineStr">
@@ -1333,16 +1524,18 @@
         </is>
       </c>
       <c r="B4" s="44" t="n">
-        <v>0.039051945</v>
+        <v>0.03952</v>
       </c>
       <c r="C4" s="52">
         <f>IFERROR(B4/B3-1,"")</f>
         <v/>
       </c>
       <c r="D4" s="45" t="n">
-        <v>640000</v>
-      </c>
-      <c r="E4" s="46" t="n"/>
+        <v>3642631.45</v>
+      </c>
+      <c r="E4" s="46" t="n">
+        <v>50.1122</v>
+      </c>
       <c r="F4" s="47" t="n">
         <v>5e-05</v>
       </c>
@@ -1353,7 +1546,7 @@
         <v>5e-05</v>
       </c>
       <c r="I4" s="48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L4" s="45" t="n">
         <v>4400000</v>
@@ -1393,6 +1586,38 @@
         <f>IF(OR(AB4="",D4="",D4=0),"",AB4/D4)</f>
         <v/>
       </c>
+      <c r="AP4" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.04165</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.03779</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.03952</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="28">
       <c r="A5" s="43" t="inlineStr">
@@ -1401,17 +1626,17 @@
         </is>
       </c>
       <c r="B5" s="44" t="n">
-        <v>0.037334818</v>
+        <v>0.03696</v>
       </c>
       <c r="C5" s="52">
         <f>IFERROR(B5/B4-1,"")</f>
         <v/>
       </c>
       <c r="D5" s="27" t="n">
-        <v>2700000</v>
+        <v>892507.65</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>0.4808</v>
+        <v>48.0929</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>5e-05</v>
@@ -1464,6 +1689,38 @@
         <v/>
       </c>
       <c r="AN5" s="51" t="n"/>
+      <c r="AP5" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.03796</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.03662</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.03696</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
@@ -1472,20 +1729,20 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.036629256</v>
+        <v>0.03653</v>
       </c>
       <c r="C6" s="27">
         <f>IFERROR(B6/B5-1,"")</f>
         <v/>
       </c>
       <c r="D6" s="27" t="n">
-        <v>2400000</v>
+        <v>807345.17</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>0.495</v>
+        <v>49.522</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>8.3841667e-05</v>
+        <v>8.384e-05</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>5e-05</v>
@@ -1532,6 +1789,38 @@
         <f>IF(OR(AB6="",D6="",D6=0),"",AB6/D6)</f>
         <v/>
       </c>
+      <c r="AP6" t="n">
+        <v>0.03695</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.03653</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="28">
       <c r="A7" s="35" t="inlineStr">
@@ -1540,20 +1829,20 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.035876632</v>
+        <v>0.03545</v>
       </c>
       <c r="C7" s="27">
         <f>IFERROR(B7/B6-1,"")</f>
         <v/>
       </c>
       <c r="D7" s="27" t="n">
-        <v>2800000</v>
+        <v>940304.27</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>0.5059</v>
+        <v>50.6072</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>5.5305e-05</v>
+        <v>5.531e-05</v>
       </c>
       <c r="G7" s="27" t="n">
         <v>5e-05</v>
@@ -1600,6 +1889,38 @@
         <f>IF(OR(AB7="",D7="",D7=0),"",AB7/D7)</f>
         <v/>
       </c>
+      <c r="AP7" t="n">
+        <v>0.03653</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.03659</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
@@ -1608,17 +1929,17 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.036271696</v>
+        <v>0.03638</v>
       </c>
       <c r="C8" s="27">
         <f>IFERROR(B8/B7-1,"")</f>
         <v/>
       </c>
       <c r="D8" s="27" t="n">
-        <v>6000000</v>
+        <v>2011221.11</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>0.4452</v>
+        <v>44.7099</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>5e-05</v>
@@ -1668,6 +1989,38 @@
         <f>IF(OR(AB8="",D8="",D8=0),"",AB8/D8)</f>
         <v/>
       </c>
+      <c r="AP8" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.03777</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.03408</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
@@ -1676,20 +2029,20 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.036327893</v>
+        <v>0.03699</v>
       </c>
       <c r="C9" s="27">
         <f>IFERROR(B9/B8-1,"")</f>
         <v/>
       </c>
       <c r="D9" s="27" t="n">
-        <v>3800000</v>
+        <v>1274468.45</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>0.5228</v>
+        <v>52.3134</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>5.0423333e-05</v>
+        <v>5.042e-05</v>
       </c>
       <c r="G9" s="27" t="n">
         <v>5e-05</v>
@@ -1747,6 +2100,38 @@
         <f>IF(OR(AB9="",D9="",D9=0),"",AB9/D9)</f>
         <v/>
       </c>
+      <c r="AP9" t="n">
+        <v>0.03639</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.03699</v>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
@@ -1755,20 +2140,20 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.038583119</v>
+        <v>0.03764</v>
       </c>
       <c r="C10" s="27">
         <f>IFERROR(B10/B9-1,"")</f>
         <v/>
       </c>
       <c r="D10" s="27" t="n">
-        <v>49000000</v>
+        <v>16420711.54</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>0.4807</v>
+        <v>48.0332</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>0.00010747667</v>
+        <v>0.00010748</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>5e-05</v>
@@ -1826,6 +2211,38 @@
         <f>IF(OR(AB10="",D10="",D10=0),"",AB10/D10)</f>
         <v/>
       </c>
+      <c r="AP10" t="n">
+        <v>0.03699</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.04539</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.03101</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
@@ -1834,20 +2251,20 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.037317882</v>
+        <v>0.03738</v>
       </c>
       <c r="C11" s="27">
         <f>IFERROR(B11/B10-1,"")</f>
         <v/>
       </c>
       <c r="D11" s="27" t="n">
-        <v>7500000</v>
+        <v>2489685.2</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>0.4561</v>
+        <v>45.6253</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>6.4706667e-05</v>
+        <v>6.471e-05</v>
       </c>
       <c r="G11" s="27" t="n">
         <v>5e-05</v>
@@ -1905,6 +2322,38 @@
         <f>IF(OR(AB11="",D11="",D11=0),"",AB11/D11)</f>
         <v/>
       </c>
+      <c r="AP11" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.03881</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.03597</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.03738</v>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
@@ -1913,17 +2362,17 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.037265172</v>
+        <v>0.03746</v>
       </c>
       <c r="C12" s="27">
         <f>IFERROR(B12/B11-1,"")</f>
         <v/>
       </c>
       <c r="D12" s="27" t="n">
-        <v>5200000</v>
+        <v>1743387.93</v>
       </c>
       <c r="E12" s="27" t="n">
-        <v>0.4699</v>
+        <v>46.9719</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>5e-05</v>
@@ -1984,6 +2433,38 @@
         <f>IF(OR(AB12="",D12="",D12=0),"",AB12/D12)</f>
         <v/>
       </c>
+      <c r="AP12" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.03839</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.03611</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
@@ -1992,17 +2473,17 @@
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.0374424</v>
+        <v>0.03737</v>
       </c>
       <c r="C13" s="27">
         <f>IFERROR(B13/B12-1,"")</f>
         <v/>
       </c>
       <c r="D13" s="27" t="n">
-        <v>4000000</v>
+        <v>1340273.11</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>0.4971</v>
+        <v>49.7168</v>
       </c>
       <c r="F13" s="27" t="n">
         <v>5e-05</v>
@@ -2063,6 +2544,38 @@
         <f>IF(OR(AB13="",D13="",D13=0),"",AB13/D13)</f>
         <v/>
       </c>
+      <c r="AP13" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.03614</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
@@ -2071,17 +2584,17 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.036042854</v>
+        <v>0.03584</v>
       </c>
       <c r="C14" s="27">
         <f>IFERROR(B14/B13-1,"")</f>
         <v/>
       </c>
       <c r="D14" s="27" t="n">
-        <v>4400000</v>
+        <v>1480409.07</v>
       </c>
       <c r="E14" s="27" t="n">
-        <v>0.4848</v>
+        <v>48.4934</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>5e-05</v>
@@ -2142,6 +2655,38 @@
         <f>IF(OR(AB14="",D14="",D14=0),"",AB14/D14)</f>
         <v/>
       </c>
+      <c r="AP14" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.03769</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.03474</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.03584</v>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
@@ -2150,17 +2695,17 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.035353279</v>
+        <v>0.03595</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(B15/B14-1,"")</f>
         <v/>
       </c>
       <c r="D15" s="27" t="n">
-        <v>6100000</v>
+        <v>2034058.39</v>
       </c>
       <c r="E15" s="27" t="n">
-        <v>0.5229</v>
+        <v>52.336</v>
       </c>
       <c r="F15" s="27" t="n">
         <v>5e-05</v>
@@ -2221,6 +2766,38 @@
         <f>IF(OR(AB15="",D15="",D15=0),"",AB15/D15)</f>
         <v/>
       </c>
+      <c r="AP15" t="n">
+        <v>0.03583</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.03636</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.03347</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.03595</v>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
@@ -2229,17 +2806,17 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>0.035939983</v>
+        <v>0.03466</v>
       </c>
       <c r="C16" s="27">
         <f>IFERROR(B16/B15-1,"")</f>
         <v/>
       </c>
       <c r="D16" s="27" t="n">
-        <v>5900000</v>
+        <v>1969055.51</v>
       </c>
       <c r="E16" s="27" t="n">
-        <v>0.5105</v>
+        <v>51.1537</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>5e-05</v>
@@ -2300,6 +2877,38 @@
         <f>IF(OR(AB16="",D16="",D16=0),"",AB16/D16)</f>
         <v/>
       </c>
+      <c r="AP16" t="n">
+        <v>0.03597</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.03801</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.03466</v>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
@@ -2308,17 +2917,17 @@
         </is>
       </c>
       <c r="B17" s="27" t="n">
-        <v>0.035326088</v>
+        <v>0.03548</v>
       </c>
       <c r="C17" s="27">
         <f>IFERROR(B17/B16-1,"")</f>
         <v/>
       </c>
       <c r="D17" s="27" t="n">
-        <v>2600000</v>
+        <v>873902.34</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>0.5034</v>
+        <v>50.3547</v>
       </c>
       <c r="F17" s="27" t="n">
         <v>5e-05</v>
@@ -2379,6 +2988,38 @@
         <f>IF(OR(AB17="",D17="",D17=0),"",AB17/D17)</f>
         <v/>
       </c>
+      <c r="AP17" t="n">
+        <v>0.03466</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
@@ -2387,17 +3028,17 @@
         </is>
       </c>
       <c r="B18" s="27" t="n">
-        <v>0.037732042</v>
+        <v>0.03648</v>
       </c>
       <c r="C18" s="27">
         <f>IFERROR(B18/B17-1,"")</f>
         <v/>
       </c>
       <c r="D18" s="27" t="n">
-        <v>12000000</v>
+        <v>4097507.07</v>
       </c>
       <c r="E18" s="27" t="n">
-        <v>0.4869</v>
+        <v>48.6653</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>5e-05</v>
@@ -2458,6 +3099,38 @@
         <f>IF(OR(AB18="",D18="",D18=0),"",AB18/D18)</f>
         <v/>
       </c>
+      <c r="AP18" t="n">
+        <v>0.03547</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.04045</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.03476</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.03648</v>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
@@ -2466,20 +3139,20 @@
         </is>
       </c>
       <c r="B19" s="27" t="n">
-        <v>0.04177344</v>
+        <v>0.04138</v>
       </c>
       <c r="C19" s="27">
         <f>IFERROR(B19/B18-1,"")</f>
         <v/>
       </c>
       <c r="D19" s="27" t="n">
-        <v>60000000</v>
+        <v>19934606.68</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>0.4862</v>
+        <v>48.6493</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>8.3426667e-05</v>
+        <v>8.343000000000001e-05</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>5e-05</v>
@@ -2537,6 +3210,38 @@
         <f>IF(OR(AB19="",D19="",D19=0),"",AB19/D19)</f>
         <v/>
       </c>
+      <c r="AP19" t="n">
+        <v>0.03651</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.04399</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.03585</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
@@ -2545,20 +3250,20 @@
         </is>
       </c>
       <c r="B20" s="27" t="n">
-        <v>0.041313538</v>
+        <v>0.041</v>
       </c>
       <c r="C20" s="27">
         <f>IFERROR(B20/B19-1,"")</f>
         <v/>
       </c>
       <c r="D20" s="27" t="n">
-        <v>59000000</v>
+        <v>14885247.2</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>0.4859</v>
+        <v>48.6569</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>8.720833299999999e-05</v>
+        <v>8.721e-05</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>5e-05</v>
@@ -2616,6 +3321,38 @@
         <f>IF(OR(AB20="",D20="",D20=0),"",AB20/D20)</f>
         <v/>
       </c>
+      <c r="AP20" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.03862</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
@@ -2624,17 +3361,17 @@
         </is>
       </c>
       <c r="B21" s="27" t="n">
-        <v>0.041629482</v>
+        <v>0.04231</v>
       </c>
       <c r="C21" s="27">
         <f>IFERROR(B21/B20-1,"")</f>
         <v/>
       </c>
       <c r="D21" s="27" t="n">
-        <v>15000000</v>
+        <v>3718616.66</v>
       </c>
       <c r="E21" s="27" t="n">
-        <v>0.4645</v>
+        <v>46.4869</v>
       </c>
       <c r="F21" s="27" t="n">
         <v>8.132e-05</v>
@@ -2695,6 +3432,38 @@
         <f>IF(OR(AB21="",D21="",D21=0),"",AB21/D21)</f>
         <v/>
       </c>
+      <c r="AP21" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.04231</v>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
@@ -2703,20 +3472,20 @@
         </is>
       </c>
       <c r="B22" s="27" t="n">
-        <v>0.043054506</v>
+        <v>0.04412</v>
       </c>
       <c r="C22" s="27">
         <f>IFERROR(B22/B21-1,"")</f>
         <v/>
       </c>
       <c r="D22" s="27" t="n">
-        <v>11000000</v>
+        <v>2819290.51</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>0.5265</v>
+        <v>52.6634</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>7.4241667e-05</v>
+        <v>7.423999999999999e-05</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>5e-05</v>
@@ -2774,6 +3543,38 @@
         <f>IF(OR(AB22="",D22="",D22=0),"",AB22/D22)</f>
         <v/>
       </c>
+      <c r="AP22" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.04444</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.04146</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
@@ -2782,20 +3583,20 @@
         </is>
       </c>
       <c r="B23" s="27" t="n">
-        <v>0.051320417</v>
+        <v>0.05111</v>
       </c>
       <c r="C23" s="27">
         <f>IFERROR(B23/B22-1,"")</f>
         <v/>
       </c>
       <c r="D23" s="27" t="n">
-        <v>150000000</v>
+        <v>36953592.44</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>0.5038</v>
+        <v>50.4205</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>9.183833299999999e-05</v>
+        <v>9.184e-05</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>5e-05</v>
@@ -2853,6 +3654,38 @@
         <f>IF(OR(AB23="",D23="",D23=0),"",AB23/D23)</f>
         <v/>
       </c>
+      <c r="AP23" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
@@ -2861,20 +3694,20 @@
         </is>
       </c>
       <c r="B24" s="27" t="n">
-        <v>0.058786904</v>
+        <v>0.06121</v>
       </c>
       <c r="C24" s="27">
         <f>IFERROR(B24/B23-1,"")</f>
         <v/>
       </c>
       <c r="D24" s="27" t="n">
-        <v>590000000</v>
+        <v>147663740.34</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>0.5178</v>
+        <v>51.813</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>7.3373333e-05</v>
+        <v>7.337e-05</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>5e-05</v>
@@ -2932,6 +3765,38 @@
         <f>IF(OR(AB24="",D24="",D24=0),"",AB24/D24)</f>
         <v/>
       </c>
+      <c r="AP24" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.06464</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.05102</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.06121</v>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
@@ -2940,17 +3805,17 @@
         </is>
       </c>
       <c r="B25" s="27" t="n">
-        <v>0.068170362</v>
+        <v>0.07048</v>
       </c>
       <c r="C25" s="27">
         <f>IFERROR(B25/B24-1,"")</f>
         <v/>
       </c>
       <c r="D25" s="27" t="n">
-        <v>1700000000</v>
+        <v>431990524.53</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>0.5117</v>
+        <v>51.2656</v>
       </c>
       <c r="F25" s="27" t="n">
         <v>5e-05</v>
@@ -3011,6 +3876,38 @@
         <f>IF(OR(AB25="",D25="",D25=0),"",AB25/D25)</f>
         <v/>
       </c>
+      <c r="AP25" t="n">
+        <v>0.06121</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.04705</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.07048</v>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
@@ -3019,20 +3916,20 @@
         </is>
       </c>
       <c r="B26" s="27" t="n">
-        <v>0.09125536099999999</v>
+        <v>0.11112</v>
       </c>
       <c r="C26" s="27">
         <f>IFERROR(B26/B25-1,"")</f>
         <v/>
       </c>
       <c r="D26" s="27" t="n">
-        <v>1900000000</v>
+        <v>480069661.1</v>
       </c>
       <c r="E26" s="27" t="n">
-        <v>0.5094</v>
+        <v>51.0543</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>5.3678333e-05</v>
+        <v>5.368e-05</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>5e-05</v>
@@ -3090,6 +3987,38 @@
         <f>IF(OR(AB26="",D26="",D26=0),"",AB26/D26)</f>
         <v/>
       </c>
+      <c r="AP26" t="n">
+        <v>0.07049</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.06454</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.11112</v>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
@@ -3098,20 +4027,20 @@
         </is>
       </c>
       <c r="B27" s="27" t="n">
-        <v>0.16670335</v>
+        <v>0.22587</v>
       </c>
       <c r="C27" s="27">
         <f>IFERROR(B27/B26-1,"")</f>
         <v/>
       </c>
       <c r="D27" s="27" t="n">
-        <v>6500000000</v>
+        <v>1618325596.67</v>
       </c>
       <c r="E27" s="27" t="n">
-        <v>0.5105</v>
+        <v>51.1304</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>3.5783333e-05</v>
+        <v>3.578e-05</v>
       </c>
       <c r="G27" s="27" t="n">
         <v>-6.06e-06</v>
@@ -3169,6 +4098,38 @@
         <f>IF(OR(AB27="",D27="",D27=0),"",AB27/D27)</f>
         <v/>
       </c>
+      <c r="AP27" t="n">
+        <v>0.11112</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.09421</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.22587</v>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
@@ -3177,17 +4138,17 @@
         </is>
       </c>
       <c r="B28" s="27" t="n">
-        <v>0.26363722</v>
+        <v>0.26721</v>
       </c>
       <c r="C28" s="27">
         <f>IFERROR(B28/B27-1,"")</f>
         <v/>
       </c>
       <c r="D28" s="27" t="n">
-        <v>5400000000</v>
+        <v>1348736173.68</v>
       </c>
       <c r="E28" s="27" t="n">
-        <v>0.5141</v>
+        <v>51.4428</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>5e-05</v>
@@ -3248,6 +4209,38 @@
         <f>IF(OR(AB28="",D28="",D28=0),"",AB28/D28)</f>
         <v/>
       </c>
+      <c r="AP28" t="n">
+        <v>0.22591</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.26721</v>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
@@ -3256,20 +4249,20 @@
         </is>
       </c>
       <c r="B29" s="27" t="n">
-        <v>0.19117724</v>
+        <v>0.1824</v>
       </c>
       <c r="C29" s="27">
         <f>IFERROR(B29/B28-1,"")</f>
         <v/>
       </c>
       <c r="D29" s="27" t="n">
-        <v>5600000000</v>
+        <v>1397360675.11</v>
       </c>
       <c r="E29" s="27" t="n">
-        <v>0.5038</v>
+        <v>50.6148</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>3.9018333e-05</v>
+        <v>3.902e-05</v>
       </c>
       <c r="G29" s="27" t="n">
         <v>-2.382e-05</v>
@@ -3327,6 +4320,38 @@
         <f>IF(OR(AB29="",D29="",D29=0),"",AB29/D29)</f>
         <v/>
       </c>
+      <c r="AP29" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.13123</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
@@ -3335,20 +4360,20 @@
         </is>
       </c>
       <c r="B30" s="27" t="n">
-        <v>0.18066321</v>
+        <v>0.23043</v>
       </c>
       <c r="C30" s="27">
         <f>IFERROR(B30/B29-1,"")</f>
         <v/>
       </c>
       <c r="D30" s="27" t="n">
-        <v>4900000000</v>
+        <v>1226575074.35</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>0.5042</v>
+        <v>50.5554</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>-2.2916667e-06</v>
+        <v>-2.29e-06</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>-0.00026375</v>
@@ -3406,6 +4431,38 @@
         <f>IF(OR(AB30="",D30="",D30=0),"",AB30/D30)</f>
         <v/>
       </c>
+      <c r="AP30" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.11758</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.23043</v>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
@@ -3414,17 +4471,17 @@
         </is>
       </c>
       <c r="B31" s="27" t="n">
-        <v>0.24723658</v>
+        <v>0.27455</v>
       </c>
       <c r="C31" s="27">
         <f>IFERROR(B31/B30-1,"")</f>
         <v/>
       </c>
       <c r="D31" s="27" t="n">
-        <v>3600000000</v>
+        <v>889491191.6799999</v>
       </c>
       <c r="E31" s="27" t="n">
-        <v>0.5056</v>
+        <v>50.616</v>
       </c>
       <c r="F31" s="27" t="n">
         <v>5e-05</v>
@@ -3439,7 +4496,7 @@
         <v>6</v>
       </c>
       <c r="L31" s="27" t="n">
-        <v>41000000</v>
+        <v>41309303.73330327</v>
       </c>
       <c r="O31" s="27" t="n">
         <v>1.3625</v>
@@ -3485,6 +4542,38 @@
         <f>IF(OR(AB31="",D31="",D31=0),"",AB31/D31)</f>
         <v/>
       </c>
+      <c r="AP31" t="n">
+        <v>0.23048</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.21352</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.27455</v>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
@@ -3493,17 +4582,17 @@
         </is>
       </c>
       <c r="B32" s="27" t="n">
-        <v>0.28338896</v>
+        <v>0.30136</v>
       </c>
       <c r="C32" s="27">
         <f>IFERROR(B32/B31-1,"")</f>
         <v/>
       </c>
       <c r="D32" s="27" t="n">
-        <v>4300000000</v>
+        <v>911357136.6900001</v>
       </c>
       <c r="E32" s="27" t="n">
-        <v>0.5079</v>
+        <v>50.8528</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>5e-05</v>
@@ -3518,7 +4607,7 @@
         <v>6</v>
       </c>
       <c r="L32" s="27" t="n">
-        <v>51000000</v>
+        <v>51120851.9571</v>
       </c>
       <c r="O32" s="27" t="n">
         <v>1.3077</v>
@@ -3564,6 +4653,38 @@
         <f>IF(OR(AB32="",D32="",D32=0),"",AB32/D32)</f>
         <v/>
       </c>
+      <c r="AP32" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
@@ -3572,20 +4693,20 @@
         </is>
       </c>
       <c r="B33" s="27" t="n">
-        <v>0.32210496</v>
+        <v>0.34658</v>
       </c>
       <c r="C33" s="27">
         <f>IFERROR(B33/B32-1,"")</f>
         <v/>
       </c>
       <c r="D33" s="27" t="n">
-        <v>1900000000</v>
+        <v>723351330.2</v>
       </c>
       <c r="E33" s="27" t="n">
-        <v>0.5155999999999999</v>
+        <v>51.6257</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>3.8363333e-05</v>
+        <v>3.836e-05</v>
       </c>
       <c r="G33" s="27" t="n">
         <v>-1.982e-05</v>
@@ -3597,7 +4718,7 @@
         <v>6</v>
       </c>
       <c r="L33" s="27" t="n">
-        <v>59000000</v>
+        <v>58824098.536428</v>
       </c>
       <c r="O33" s="27" t="n">
         <v>1.3167</v>
@@ -3643,6 +4764,38 @@
         <f>IF(OR(AB33="",D33="",D33=0),"",AB33/D33)</f>
         <v/>
       </c>
+      <c r="AP33" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
@@ -3651,23 +4804,23 @@
         </is>
       </c>
       <c r="B34" s="27" t="n">
-        <v>0.3685</v>
+        <v>0.37932</v>
       </c>
       <c r="C34" s="27">
         <f>IFERROR(B34/B33-1,"")</f>
         <v/>
       </c>
       <c r="D34" s="27" t="n">
-        <v>721232744</v>
+        <v>721232744.5</v>
       </c>
       <c r="E34" s="27" t="n">
-        <v>51.21</v>
+        <v>51.2117</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>4.9e-05</v>
+        <v>4.932e-05</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>4.6e-05</v>
+        <v>4.59e-05</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>5e-05</v>
@@ -3676,7 +4829,7 @@
         <v>6</v>
       </c>
       <c r="L34" s="27" t="n">
-        <v>63358945</v>
+        <v>63358945.46969228</v>
       </c>
       <c r="O34" s="27" t="n">
         <v>1.31</v>
@@ -3732,6 +4885,38 @@
           <t>hau-markup, phan phoi dang chay</t>
         </is>
       </c>
+      <c r="AP34" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
@@ -3740,23 +4925,23 @@
         </is>
       </c>
       <c r="B35" s="27" t="n">
-        <v>0.4128</v>
+        <v>0.33984</v>
       </c>
       <c r="C35" s="27">
         <f>IFERROR(B35/B34-1,"")</f>
         <v/>
       </c>
       <c r="D35" s="27" t="n">
-        <v>1529118313</v>
+        <v>1529118312.82</v>
       </c>
       <c r="E35" s="27" t="n">
-        <v>50.85</v>
+        <v>50.8455</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>3.3e-05</v>
+        <v>3.283e-05</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>-2e-06</v>
+        <v>-2.2e-06</v>
       </c>
       <c r="H35" s="27" t="n">
         <v>5e-05</v>
@@ -3765,10 +4950,10 @@
         <v>6</v>
       </c>
       <c r="L35" s="27" t="n">
-        <v>70833437</v>
+        <v>70833436.93880001</v>
       </c>
       <c r="O35" s="27" t="n">
-        <v>1.3036</v>
+        <v>1.3035</v>
       </c>
       <c r="P35" s="27" t="n">
         <v>0.333</v>
@@ -3816,6 +5001,38 @@
         <f>IF(OR(AB35="",D35="",D35=0),"",AB35/D35)</f>
         <v/>
       </c>
+      <c r="AP35" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.67205</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
@@ -3824,17 +5041,41 @@
         </is>
       </c>
       <c r="B36" s="27" t="n">
-        <v>0.2858</v>
+        <v>0.21714</v>
       </c>
       <c r="C36" s="27">
         <f>IFERROR(B36/B35-1,"")</f>
         <v/>
       </c>
+      <c r="D36" s="27" t="n">
+        <v>1152230682.26</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>50.2726</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>-8.351000000000001e-05</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>-0.00057862</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>5e-05</v>
+      </c>
       <c r="I36" s="27" t="n">
         <v>6</v>
       </c>
       <c r="L36" s="27" t="n">
-        <v>39769000</v>
+        <v>39768928.88008608</v>
+      </c>
+      <c r="O36" s="27" t="n">
+        <v>1.6178</v>
+      </c>
+      <c r="P36" s="27" t="n">
+        <v>0.5576</v>
+      </c>
+      <c r="Q36" s="27" t="n">
+        <v>0.6207</v>
       </c>
       <c r="R36" s="27">
         <f>IFERROR(O36/P36,"")</f>
@@ -3886,6 +5127,38 @@
           <t>px -31%, OI -44% — suppressor dung bai</t>
         </is>
       </c>
+      <c r="AP36" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.21714</v>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
@@ -3894,20 +5167,20 @@
         </is>
       </c>
       <c r="B37" s="27" t="n">
-        <v>0.1713490368477554</v>
+        <v>0.17216</v>
       </c>
       <c r="C37" s="27">
         <f>IFERROR(B37/B36-1,"")</f>
         <v/>
       </c>
       <c r="D37" s="27" t="n">
-        <v>738355605.75427</v>
+        <v>738355605.75</v>
       </c>
       <c r="E37" s="27" t="n">
-        <v>49.892268</v>
+        <v>49.9157</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>-0.000988205</v>
+        <v>-0.00098821</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>-0.00205082</v>
@@ -3965,6 +5238,38 @@
         <f>IF(OR(AB37="",D37="",D37=0),"",AB37/D37)</f>
         <v/>
       </c>
+      <c r="AP37" t="n">
+        <v>0.21714</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.22437</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.13306</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.17216</v>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
@@ -3973,20 +5278,20 @@
         </is>
       </c>
       <c r="B38" s="27" t="n">
-        <v>0.0887329722906726</v>
+        <v>0.06101</v>
       </c>
       <c r="C38" s="27">
         <f>IFERROR(B38/B37-1,"")</f>
         <v/>
       </c>
       <c r="D38" s="27" t="n">
-        <v>1039593900.21891</v>
+        <v>1039593900.22</v>
       </c>
       <c r="E38" s="27" t="n">
-        <v>49.166328</v>
+        <v>49.1464</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>-0.003337582</v>
+        <v>-0.00333758</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>-0.02</v>
@@ -4044,6 +5349,38 @@
         <f>IF(OR(AB38="",D38="",D38=0),"",AB38/D38)</f>
         <v/>
       </c>
+      <c r="AP38" t="n">
+        <v>0.17216</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.05417</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.06101</v>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
@@ -4052,20 +5389,20 @@
         </is>
       </c>
       <c r="B39" s="27" t="n">
-        <v>0.0630603801681764</v>
+        <v>0.0575</v>
       </c>
       <c r="C39" s="27">
         <f>IFERROR(B39/B38-1,"")</f>
         <v/>
       </c>
       <c r="D39" s="27" t="n">
-        <v>562696137.64149</v>
+        <v>562696137.64</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>49.155989</v>
+        <v>49.1862</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>-0.001911111666666667</v>
+        <v>-0.00191111</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>-0.00438872</v>
@@ -4123,6 +5460,38 @@
         <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
         <v/>
       </c>
+      <c r="AP39" t="n">
+        <v>0.06101</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.07698000000000001</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="58" t="inlineStr">
@@ -4131,25 +5500,25 @@
         </is>
       </c>
       <c r="B40" s="59" t="n">
-        <v>0.056915</v>
+        <v>0.05078</v>
       </c>
       <c r="C40" s="57" t="n">
         <v>-0.09745231715678249</v>
       </c>
       <c r="D40" s="57" t="n">
-        <v>253304478</v>
+        <v>253304478.25</v>
       </c>
       <c r="E40" s="57" t="n">
-        <v>0.4804</v>
+        <v>48.1283</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>-0.000806</v>
+        <v>-0.00080634</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>-0.002363</v>
+        <v>-0.00236339</v>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-0.000139</v>
+        <v>-0.0001387</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>24</v>
@@ -4161,7 +5530,7 @@
       </c>
       <c r="K40" s="56" t="n"/>
       <c r="L40" s="27" t="n">
-        <v>18027284</v>
+        <v>18027284.00233</v>
       </c>
       <c r="O40" s="27" t="n">
         <v>1.1805</v>
@@ -4189,6 +5558,38 @@
       <c r="AC40" s="27" t="n">
         <v>0.462</v>
       </c>
+      <c r="AP40" t="n">
+        <v>0.05749</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.06766</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="58" t="inlineStr">
@@ -4197,25 +5598,25 @@
         </is>
       </c>
       <c r="B41" s="59" t="n">
-        <v>0.047883</v>
+        <v>0.04469</v>
       </c>
       <c r="C41" s="57" t="n">
         <v>-0.1586927874901168</v>
       </c>
       <c r="D41" s="57" t="n">
-        <v>172554826</v>
+        <v>172554826.27</v>
       </c>
       <c r="E41" s="57" t="n">
-        <v>0.4791</v>
+        <v>47.9659</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>-0.000349</v>
+        <v>-0.00034904</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>-0.000722</v>
+        <v>-0.0007222799999999999</v>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-9.66e-05</v>
+        <v>-9.664e-05</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>24</v>
@@ -4227,7 +5628,7 @@
       </c>
       <c r="K41" s="56" t="n"/>
       <c r="L41" s="27" t="n">
-        <v>17469390</v>
+        <v>17469389.52912</v>
       </c>
       <c r="O41" s="27" t="n">
         <v>1.3197</v>
@@ -4255,6 +5656,38 @@
       <c r="AC41" s="27" t="n">
         <v>0.493</v>
       </c>
+      <c r="AP41" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.04334</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.04469</v>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="58" t="inlineStr">
@@ -4263,22 +5696,22 @@
         </is>
       </c>
       <c r="B42" s="59" t="n">
-        <v>0.043163</v>
+        <v>0.04419</v>
       </c>
       <c r="C42" s="57" t="n">
         <v>-0.09857360649917513</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>143022585</v>
+        <v>143022584.96</v>
       </c>
       <c r="E42" s="57" t="n">
-        <v>0.4883</v>
+        <v>48.8532</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>-0.000186</v>
+        <v>-0.00018606</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>-0.000821</v>
+        <v>-0.0008210099999999999</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>3.5e-06</v>
@@ -4293,7 +5726,7 @@
       </c>
       <c r="K42" s="56" t="n"/>
       <c r="L42" s="27" t="n">
-        <v>17252550</v>
+        <v>17252549.66741332</v>
       </c>
       <c r="O42" s="27" t="n">
         <v>1.3123</v>
@@ -4321,6 +5754,38 @@
       <c r="AC42" s="27" t="n">
         <v>0.481</v>
       </c>
+      <c r="AP42" t="n">
+        <v>0.04469</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.04652</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.04419</v>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="58" t="inlineStr">
@@ -4329,22 +5794,22 @@
         </is>
       </c>
       <c r="B43" s="59" t="n">
-        <v>0.051353</v>
+        <v>0.05244</v>
       </c>
       <c r="C43" s="57" t="n">
         <v>0.1897458471375948</v>
       </c>
       <c r="D43" s="57" t="n">
-        <v>471564742</v>
+        <v>471564741.66</v>
       </c>
       <c r="E43" s="57" t="n">
-        <v>0.4906</v>
+        <v>49.1287</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>-0.000548</v>
+        <v>-0.0005479699999999999</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>-0.002347</v>
+        <v>-0.00234724</v>
       </c>
       <c r="H43" s="27" t="n">
         <v>1.25e-05</v>
@@ -4359,7 +5824,7 @@
       </c>
       <c r="K43" s="56" t="n"/>
       <c r="L43" s="27" t="n">
-        <v>17356910</v>
+        <v>17356910.29415</v>
       </c>
       <c r="O43" s="27" t="n">
         <v>1.3135</v>
@@ -4387,6 +5852,38 @@
       <c r="AC43" s="27" t="n">
         <v>0.483</v>
       </c>
+      <c r="AP43" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.06186</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.05244</v>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="60" t="inlineStr">
@@ -4395,21 +5892,29 @@
         </is>
       </c>
       <c r="B44" s="61" t="n">
-        <v>0.0519</v>
+        <v>0.04311</v>
       </c>
       <c r="C44" s="62" t="n">
         <v>0.01065176328549455</v>
       </c>
       <c r="D44" s="62" t="n">
-        <v>102200000</v>
+        <v>226476484.35</v>
       </c>
       <c r="E44" s="62" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="F44" s="63" t="n"/>
-      <c r="G44" s="63" t="n"/>
-      <c r="H44" s="63" t="n"/>
-      <c r="I44" s="63" t="n"/>
+        <v>48.5283</v>
+      </c>
+      <c r="F44" s="63" t="n">
+        <v>-5.587e-05</v>
+      </c>
+      <c r="G44" s="63" t="n">
+        <v>-0.00034965</v>
+      </c>
+      <c r="H44" s="63" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I44" s="63" t="n">
+        <v>10</v>
+      </c>
       <c r="J44" s="63" t="inlineStr">
         <is>
           <t>near_zero</t>
@@ -4417,16 +5922,18 @@
       </c>
       <c r="K44" s="64" t="n"/>
       <c r="L44" s="63" t="n">
-        <v>18070000</v>
+        <v>18068851.38786</v>
       </c>
       <c r="M44" s="63" t="n"/>
       <c r="N44" s="63" t="n"/>
       <c r="O44" s="63" t="n">
-        <v>1.199</v>
-      </c>
-      <c r="P44" s="63" t="n"/>
+        <v>1.1988</v>
+      </c>
+      <c r="P44" s="63" t="n">
+        <v>1.6357</v>
+      </c>
       <c r="Q44" s="63" t="n">
-        <v>1.396</v>
+        <v>1.3958</v>
       </c>
       <c r="R44" s="63" t="n"/>
       <c r="S44" s="63" t="n"/>
@@ -4462,6 +5969,38 @@
       <c r="AM44" s="63" t="n"/>
       <c r="AN44" s="63" t="n"/>
       <c r="AO44" s="63" t="n"/>
+      <c r="AP44" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.05586</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.04311</v>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
@@ -4470,20 +6009,20 @@
         </is>
       </c>
       <c r="B45" s="27" t="n">
-        <v>0.0404143452896341</v>
+        <v>0.03704</v>
       </c>
       <c r="C45" s="27">
         <f>IFERROR(B45/B44-1,"")</f>
         <v/>
       </c>
       <c r="D45" s="27" t="n">
-        <v>140686649.01256</v>
+        <v>140686649.01</v>
       </c>
       <c r="E45" s="27" t="n">
-        <v>47.657681</v>
+        <v>47.6837</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>4.8475e-05</v>
+        <v>4.847e-05</v>
       </c>
       <c r="G45" s="27" t="n">
         <v>4.416e-05</v>
@@ -4530,6 +6069,38 @@
         <f>IF(OR(AB45="",D45="",D45=0),"",AB45/D45)</f>
         <v/>
       </c>
+      <c r="AP45" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0.03658</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="27" t="inlineStr">
@@ -4538,20 +6109,20 @@
         </is>
       </c>
       <c r="B46" s="27" t="n">
-        <v>0.0389331582839826</v>
+        <v>0.03895</v>
       </c>
       <c r="C46" s="27">
         <f>IFERROR(B46/B45-1,"")</f>
         <v/>
       </c>
       <c r="D46" s="27" t="n">
-        <v>42263053.84667</v>
+        <v>42263053.85</v>
       </c>
       <c r="E46" s="27" t="n">
-        <v>49.246308</v>
+        <v>49.2639</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>-9.721166666666668e-05</v>
+        <v>-9.721e-05</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>-0.00029585</v>
@@ -4598,6 +6169,38 @@
         <f>IF(OR(AB46="",D46="",D46=0),"",AB46/D46)</f>
         <v/>
       </c>
+      <c r="AP46" t="n">
+        <v>0.03932</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.04029</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0.03804</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
@@ -4606,20 +6209,20 @@
         </is>
       </c>
       <c r="B47" s="27" t="n">
-        <v>0.0373057526039732</v>
+        <v>0.03633</v>
       </c>
       <c r="C47" s="27">
         <f>IFERROR(B47/B46-1,"")</f>
         <v/>
       </c>
       <c r="D47" s="27" t="n">
-        <v>45394765.99188</v>
+        <v>45394765.99</v>
       </c>
       <c r="E47" s="27" t="n">
-        <v>46.007235</v>
+        <v>46.0331</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>-8.702333333333332e-05</v>
+        <v>-8.702e-05</v>
       </c>
       <c r="G47" s="27" t="n">
         <v>-0.00030814</v>
@@ -4666,6 +6269,38 @@
         <f>IF(OR(AB47="",D47="",D47=0),"",AB47/D47)</f>
         <v/>
       </c>
+      <c r="AP47" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0.03273</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0.03633</v>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="27" t="inlineStr">
@@ -4674,20 +6309,20 @@
         </is>
       </c>
       <c r="B48" s="27" t="n">
-        <v>0.0363926583940916</v>
+        <v>0.03981</v>
       </c>
       <c r="C48" s="27">
         <f>IFERROR(B48/B47-1,"")</f>
         <v/>
       </c>
       <c r="D48" s="27" t="n">
-        <v>54495385.01868</v>
+        <v>54495385.02</v>
       </c>
       <c r="E48" s="27" t="n">
-        <v>48.408399</v>
+        <v>48.4452</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>-0.000389125</v>
+        <v>-0.00038912</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>-0.00084272</v>
@@ -4734,6 +6369,38 @@
         <f>IF(OR(AB48="",D48="",D48=0),"",AB48/D48)</f>
         <v/>
       </c>
+      <c r="AP48" t="n">
+        <v>0.03633</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.04014</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0.03395</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.03981</v>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="27" t="inlineStr">
@@ -4742,17 +6409,17 @@
         </is>
       </c>
       <c r="B49" s="27" t="n">
-        <v>0.0373570870676163</v>
+        <v>0.03821</v>
       </c>
       <c r="C49" s="27">
         <f>IFERROR(B49/B48-1,"")</f>
         <v/>
       </c>
       <c r="D49" s="27" t="n">
-        <v>43707076.14468</v>
+        <v>43707076.14</v>
       </c>
       <c r="E49" s="27" t="n">
-        <v>48.253558</v>
+        <v>48.2849</v>
       </c>
       <c r="F49" s="27" t="n">
         <v>1.937e-05</v>
@@ -4802,6 +6469,38 @@
         <f>IF(OR(AB49="",D49="",D49=0),"",AB49/D49)</f>
         <v/>
       </c>
+      <c r="AP49" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.03944</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0.03583</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
@@ -4810,20 +6509,20 @@
         </is>
       </c>
       <c r="B50" s="27" t="n">
-        <v>0.0375901118292134</v>
+        <v>0.03694</v>
       </c>
       <c r="C50" s="27">
         <f>IFERROR(B50/B49-1,"")</f>
         <v/>
       </c>
       <c r="D50" s="27" t="n">
-        <v>28138687.39511</v>
+        <v>28138687.4</v>
       </c>
       <c r="E50" s="27" t="n">
-        <v>47.210051</v>
+        <v>47.2217</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>4.253166666666667e-05</v>
+        <v>4.253e-05</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>5.19e-06</v>
@@ -4870,73 +6569,1673 @@
         <f>IF(OR(AB50="",D50="",D50=0),"",AB50/D50)</f>
         <v/>
       </c>
+      <c r="AP50" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.03919</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0.03635792928012117</v>
-      </c>
-      <c r="C51">
+      <c r="B51" s="27" t="n">
+        <v>0.03514</v>
+      </c>
+      <c r="C51" s="27">
         <f>IFERROR(B51/B50-1,"")</f>
         <v/>
       </c>
-      <c r="D51" t="n">
-        <v>19287848.72461</v>
-      </c>
-      <c r="E51" t="n">
-        <v>46.141003</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2.4445e-05</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="D51" s="27" t="n">
+        <v>19287848.72</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <v>46.2206</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>2.445e-05</v>
+      </c>
+      <c r="G51" s="27" t="n">
         <v>-4.002e-05</v>
       </c>
-      <c r="H51" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="I51" t="n">
+      <c r="H51" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I51" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" s="27" t="n">
         <v>11251300.09384519</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51" s="27" t="n">
         <v>1.6943</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P51" s="27" t="n">
         <v>1.8466</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51" s="27" t="n">
         <v>1.4015</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="27">
         <f>IFERROR(O51/P51,"")</f>
         <v/>
       </c>
-      <c r="S51">
+      <c r="S51" s="27">
         <f>IFERROR(AVERAGE(R49:R51),"")</f>
         <v/>
       </c>
-      <c r="T51">
+      <c r="T51" s="27">
         <f>IFERROR(Q51/Q46,"")</f>
         <v/>
       </c>
-      <c r="U51">
+      <c r="U51" s="27">
         <f>IFERROR(O51/O48-1,"")</f>
         <v/>
       </c>
-      <c r="V51">
+      <c r="V51" s="27">
         <f>IFERROR(P51/P48-1,"")</f>
         <v/>
       </c>
-      <c r="AJ51">
+      <c r="AJ51" s="27">
         <f>IF(OR(AB51="",D51="",D51=0),"",AB51/D51)</f>
         <v/>
+      </c>
+      <c r="AP51" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0.03432</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0.03514</v>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="D52" s="27" t="n">
+        <v>8350835.08</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <v>51.7165</v>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0.03774</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0.03582</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="D53" s="27" t="n">
+        <v>18794321.38</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <v>49.8031</v>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>6.786e-05</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>0.00014731</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="D54" s="27" t="n">
+        <v>9855496.439999999</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <v>48.0392</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.04739</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="D55" s="27" t="n">
+        <v>2636941.15</v>
+      </c>
+      <c r="E55" s="27" t="n">
+        <v>47.1134</v>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G55" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H55" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0.03872</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="D56" s="27" t="n">
+        <v>1874627.63</v>
+      </c>
+      <c r="E56" s="27" t="n">
+        <v>45.9915</v>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0.04128</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0.03982</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="D57" s="27" t="n">
+        <v>3985295.22</v>
+      </c>
+      <c r="E57" s="27" t="n">
+        <v>50.1382</v>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H57" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="n">
+        <v>0.03963</v>
+      </c>
+      <c r="D58" s="27" t="n">
+        <v>1605180.13</v>
+      </c>
+      <c r="E58" s="27" t="n">
+        <v>47.1838</v>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H58" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0.04124</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0.04226</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0.03898</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0.03963</v>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="n">
+        <v>0.03668</v>
+      </c>
+      <c r="D59" s="27" t="n">
+        <v>2329209.38</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>43.2119</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H59" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0.03966</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>0.04026</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0.03625</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0.03668</v>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="n">
+        <v>0.03965</v>
+      </c>
+      <c r="D60" s="27" t="n">
+        <v>3714901.26</v>
+      </c>
+      <c r="E60" s="27" t="n">
+        <v>51.6431</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0.03669</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0.03636</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0.03965</v>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="n">
+        <v>0.03883</v>
+      </c>
+      <c r="D61" s="27" t="n">
+        <v>1373790</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>47.8833</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H61" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0.03855</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0.03883</v>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="n">
+        <v>0.03768</v>
+      </c>
+      <c r="D62" s="27" t="n">
+        <v>936948.9300000001</v>
+      </c>
+      <c r="E62" s="27" t="n">
+        <v>48.2275</v>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G62" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H62" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0.03739</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0.03768</v>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="n">
+        <v>0.03762</v>
+      </c>
+      <c r="D63" s="27" t="n">
+        <v>1751774.37</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <v>48.0668</v>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H63" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>0.03768</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0.03654</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0.03762</v>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="D64" s="27" t="n">
+        <v>1769820.81</v>
+      </c>
+      <c r="E64" s="27" t="n">
+        <v>52.2801</v>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G64" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H64" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I64" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>2827425.08</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <v>46.9966</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G65" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H65" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I65" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0.03643</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="D66" s="27" t="n">
+        <v>2154430.55</v>
+      </c>
+      <c r="E66" s="27" t="n">
+        <v>45.8713</v>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G66" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H66" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I66" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0.03782</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="D67" s="27" t="n">
+        <v>1744741.76</v>
+      </c>
+      <c r="E67" s="27" t="n">
+        <v>48.1488</v>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H67" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I67" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0.03641</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="D68" s="27" t="n">
+        <v>134942809.71</v>
+      </c>
+      <c r="E68" s="27" t="n">
+        <v>48.714</v>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>-0.0008636</v>
+      </c>
+      <c r="G68" s="27" t="n">
+        <v>-0.00295908</v>
+      </c>
+      <c r="H68" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I68" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L68" s="27" t="n">
+        <v>16163380.51944</v>
+      </c>
+      <c r="O68" s="27" t="n">
+        <v>1.3103</v>
+      </c>
+      <c r="P68" s="27" t="n">
+        <v>1.9949</v>
+      </c>
+      <c r="Q68" s="27" t="n">
+        <v>1.4919</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="n">
+        <v>0.04068</v>
+      </c>
+      <c r="D69" s="27" t="n">
+        <v>54216924.73</v>
+      </c>
+      <c r="E69" s="27" t="n">
+        <v>47.1035</v>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>-2.466e-05</v>
+      </c>
+      <c r="G69" s="27" t="n">
+        <v>-0.00022282</v>
+      </c>
+      <c r="H69" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I69" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L69" s="27" t="n">
+        <v>15567064.60512154</v>
+      </c>
+      <c r="O69" s="27" t="n">
+        <v>1.3906</v>
+      </c>
+      <c r="P69" s="27" t="n">
+        <v>1.9138</v>
+      </c>
+      <c r="Q69" s="27" t="n">
+        <v>1.5445</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0.04422</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0.04068</v>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="D70" s="27" t="n">
+        <v>46514939.87</v>
+      </c>
+      <c r="E70" s="27" t="n">
+        <v>47.6054</v>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>-0.00027546</v>
+      </c>
+      <c r="G70" s="27" t="n">
+        <v>-0.00035655</v>
+      </c>
+      <c r="H70" s="27" t="n">
+        <v>-0.00020599</v>
+      </c>
+      <c r="I70" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L70" s="27" t="n">
+        <v>13977596.86524</v>
+      </c>
+      <c r="O70" s="27" t="n">
+        <v>1.4798</v>
+      </c>
+      <c r="P70" s="27" t="n">
+        <v>2.1104</v>
+      </c>
+      <c r="Q70" s="27" t="n">
+        <v>1.5893</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0.04067</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0.03832</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="n">
+        <v>0.03932</v>
+      </c>
+      <c r="D71" s="27" t="n">
+        <v>105937477.36</v>
+      </c>
+      <c r="E71" s="27" t="n">
+        <v>47.3471</v>
+      </c>
+      <c r="F71" s="27" t="n">
+        <v>-0.00038953</v>
+      </c>
+      <c r="G71" s="27" t="n">
+        <v>-0.00142204</v>
+      </c>
+      <c r="H71" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I71" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L71" s="27" t="n">
+        <v>14747523.8069718</v>
+      </c>
+      <c r="O71" s="27" t="n">
+        <v>1.4616</v>
+      </c>
+      <c r="P71" s="27" t="n">
+        <v>1.9499</v>
+      </c>
+      <c r="Q71" s="27" t="n">
+        <v>1.5151</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0.04709</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0.03932</v>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="D72" s="27" t="n">
+        <v>15770198.18</v>
+      </c>
+      <c r="E72" s="27" t="n">
+        <v>48.0664</v>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>1.682e-05</v>
+      </c>
+      <c r="G72" s="27" t="n">
+        <v>-5.06e-05</v>
+      </c>
+      <c r="H72" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I72" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L72" s="27" t="n">
+        <v>10738411.55444526</v>
+      </c>
+      <c r="O72" s="27" t="n">
+        <v>1.7488</v>
+      </c>
+      <c r="P72" s="27" t="n">
+        <v>1.8744</v>
+      </c>
+      <c r="Q72" s="27" t="n">
+        <v>1.3969</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>0.03515</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0.03497</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="n">
+        <v>0.03653</v>
+      </c>
+      <c r="D73" s="27" t="n">
+        <v>22321367.8</v>
+      </c>
+      <c r="E73" s="27" t="n">
+        <v>48.3064</v>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>3.507e-05</v>
+      </c>
+      <c r="G73" s="27" t="n">
+        <v>2.32e-06</v>
+      </c>
+      <c r="H73" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I73" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L73" s="27" t="n">
+        <v>10968992.146555</v>
+      </c>
+      <c r="O73" s="27" t="n">
+        <v>1.7794</v>
+      </c>
+      <c r="P73" s="27" t="n">
+        <v>1.7709</v>
+      </c>
+      <c r="Q73" s="27" t="n">
+        <v>1.3485</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0.03561</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>0.03798</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0.03455</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>0.03653</v>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="D74" s="27" t="n">
+        <v>23241943.44</v>
+      </c>
+      <c r="E74" s="27" t="n">
+        <v>45.9539</v>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>2.55e-06</v>
+      </c>
+      <c r="G74" s="27" t="n">
+        <v>-4.367e-05</v>
+      </c>
+      <c r="H74" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I74" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" s="27" t="n">
+        <v>11220353.07173448</v>
+      </c>
+      <c r="O74" s="27" t="n">
+        <v>1.7929</v>
+      </c>
+      <c r="P74" s="27" t="n">
+        <v>1.7988</v>
+      </c>
+      <c r="Q74" s="27" t="n">
+        <v>1.3579</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>0.03653</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>0.03751</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>0.03511</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="n">
+        <v>0.03646</v>
+      </c>
+      <c r="D75" s="27" t="n">
+        <v>22377396.69</v>
+      </c>
+      <c r="E75" s="27" t="n">
+        <v>48.2712</v>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>4.597e-05</v>
+      </c>
+      <c r="G75" s="27" t="n">
+        <v>2.585e-05</v>
+      </c>
+      <c r="H75" s="27" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I75" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L75" s="27" t="n">
+        <v>10797797.3231</v>
+      </c>
+      <c r="O75" s="27" t="n">
+        <v>1.9153</v>
+      </c>
+      <c r="P75" s="27" t="n">
+        <v>1.7886</v>
+      </c>
+      <c r="Q75" s="27" t="n">
+        <v>1.3196</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>0.03691</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0.03546</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>0.03646</v>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/case_files/CASE_BANK.xlsx
+++ b/docs/case_files/CASE_BANK.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="27" min="1" max="1"/>
@@ -981,88 +981,162 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>LAYER COVERAGE (R7 21/08)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>first_nn LSR (freshwatch)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>first_nn OI (fapi 30d)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>N/A-GAP dates (freshwatch)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>2026-07-24, 2026-07-25, 2026-07-26, 2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>N/A-RETENTION rule</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Trước first_nn = N/A-RETENTION (store không cover, không collect)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>CORRECTIONS (R8 21/08)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Gap 24-26/07 nguồn store</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="27" t="inlineStr">
         <is>
           <t>3 ngày freshwatch drop toàn universe (họ TUT+BTW) — không sửa lịch sử</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Schema-migration R4 v2.1 partial</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>cols 42-45 = o/h/l/c append (append-only per L-57 R4) · cols 46-47 = vol_alpha/taker_alpha CHƯA-TRA (chờ nhịp 2 R5) · cols 51-52 = vol_spot_ext_usd/spot_ext_venue CHƯA-TRA (chờ nhịp 2 R5) · cols 48-50 reserved. Cột v1 cũ (1-41) KHÔNG đè.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>META (V5 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>v1+ext-20260821 (v1 cols 1-41 + R4 append cols 42-52 · o/h/l/c + vol_alpha CHƯA-TRA + cols 51-52 CHƯA-TRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>consumer_rule</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Consumer đọc theo HEADER row 2 field names (không hardcode col index). Cols 42+ append-only per L-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE UPDATE (V4 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>lsr_null_dates (16)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-10, 2026-06-11, 2026-06-12, 2026-06-14, 2026-06-15, 2026-06-16, 2026-06-17, 2026-06-18, 2026-06-19, 2026-06-20, 2026-06-21, 2026-06-22, 2026-06-23, 2026-06-24, 2026-06-25, 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OI first_nn (real)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OI last_nn</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1133,32 +1207,32 @@
           <t>MANUAL (operator)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="27" t="inlineStr">
         <is>
           <t>OHLC-append (R4)</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="27" t="inlineStr">
         <is>
           <t>vol_alpha-append (R4)</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="27" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="27" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="27" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="27" t="inlineStr">
         <is>
           <t>SPOT-EXT (v2.1 R4 21/08)</t>
         </is>
@@ -1370,45 +1444,45 @@
           <t>mm_note</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP2" s="27" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AQ2" s="27" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR2" s="27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" s="27" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT2" s="27" t="inlineStr">
         <is>
           <t>vol_alpha</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AU2" s="27" t="inlineStr">
         <is>
           <t>taker_alpha</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr">
+      <c r="AV2" s="27" t="inlineStr"/>
+      <c r="AW2" s="27" t="inlineStr"/>
+      <c r="AX2" s="27" t="inlineStr"/>
+      <c r="AY2" s="27" t="inlineStr">
         <is>
           <t>vol_spot_ext_usd</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" s="27" t="inlineStr">
         <is>
           <t>spot_ext_venue</t>
         </is>
@@ -1484,34 +1558,34 @@
         <v/>
       </c>
       <c r="AN3" s="51" t="n"/>
-      <c r="AP3" t="n">
+      <c r="AP3" s="27" t="n">
         <v>0.04139</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ3" s="27" t="n">
         <v>0.04463</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR3" s="27" t="n">
         <v>0.03658</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AS3" s="27" t="n">
         <v>0.03774</v>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AT3" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU3" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY3" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ3" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -1586,34 +1660,34 @@
         <f>IF(OR(AB4="",D4="",D4=0),"",AB4/D4)</f>
         <v/>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP4" s="27" t="n">
         <v>0.038</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ4" s="27" t="n">
         <v>0.04165</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AR4" s="27" t="n">
         <v>0.03779</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS4" s="27" t="n">
         <v>0.03952</v>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AT4" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU4" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AY4" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ4" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -1689,34 +1763,34 @@
         <v/>
       </c>
       <c r="AN5" s="51" t="n"/>
-      <c r="AP5" t="n">
+      <c r="AP5" s="27" t="n">
         <v>0.0375</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ5" s="27" t="n">
         <v>0.03796</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR5" s="27" t="n">
         <v>0.03662</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS5" s="27" t="n">
         <v>0.03696</v>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AT5" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU5" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AY5" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ5" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -1789,34 +1863,34 @@
         <f>IF(OR(AB6="",D6="",D6=0),"",AB6/D6)</f>
         <v/>
       </c>
-      <c r="AP6" t="n">
+      <c r="AP6" s="27" t="n">
         <v>0.03695</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ6" s="27" t="n">
         <v>0.0374</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AR6" s="27" t="n">
         <v>0.036</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AS6" s="27" t="n">
         <v>0.03653</v>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AT6" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU6" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AY6" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ6" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -1889,34 +1963,34 @@
         <f>IF(OR(AB7="",D7="",D7=0),"",AB7/D7)</f>
         <v/>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP7" s="27" t="n">
         <v>0.03653</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ7" s="27" t="n">
         <v>0.03659</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR7" s="27" t="n">
         <v>0.03529</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AS7" s="27" t="n">
         <v>0.03545</v>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AT7" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU7" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AY7" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ7" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -1989,34 +2063,34 @@
         <f>IF(OR(AB8="",D8="",D8=0),"",AB8/D8)</f>
         <v/>
       </c>
-      <c r="AP8" t="n">
+      <c r="AP8" s="27" t="n">
         <v>0.03544</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AQ8" s="27" t="n">
         <v>0.03777</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR8" s="27" t="n">
         <v>0.03408</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AS8" s="27" t="n">
         <v>0.03638</v>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AT8" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU8" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AY8" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ8" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2100,34 +2174,34 @@
         <f>IF(OR(AB9="",D9="",D9=0),"",AB9/D9)</f>
         <v/>
       </c>
-      <c r="AP9" t="n">
+      <c r="AP9" s="27" t="n">
         <v>0.03639</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ9" s="27" t="n">
         <v>0.038</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR9" s="27" t="n">
         <v>0.03527</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS9" s="27" t="n">
         <v>0.03699</v>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="AT9" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU9" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AY9" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ9" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2211,34 +2285,34 @@
         <f>IF(OR(AB10="",D10="",D10=0),"",AB10/D10)</f>
         <v/>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP10" s="27" t="n">
         <v>0.03699</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ10" s="27" t="n">
         <v>0.04539</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR10" s="27" t="n">
         <v>0.03101</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS10" s="27" t="n">
         <v>0.03764</v>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AT10" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU10" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AY10" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ10" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2322,34 +2396,34 @@
         <f>IF(OR(AB11="",D11="",D11=0),"",AB11/D11)</f>
         <v/>
       </c>
-      <c r="AP11" t="n">
+      <c r="AP11" s="27" t="n">
         <v>0.03764</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ11" s="27" t="n">
         <v>0.03881</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR11" s="27" t="n">
         <v>0.03597</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS11" s="27" t="n">
         <v>0.03738</v>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
+      <c r="AT11" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU11" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="AY11" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ11" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2433,34 +2507,34 @@
         <f>IF(OR(AB12="",D12="",D12=0),"",AB12/D12)</f>
         <v/>
       </c>
-      <c r="AP12" t="n">
+      <c r="AP12" s="27" t="n">
         <v>0.03737</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ12" s="27" t="n">
         <v>0.03839</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR12" s="27" t="n">
         <v>0.03611</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS12" s="27" t="n">
         <v>0.03746</v>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AT12" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU12" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
+      <c r="AY12" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ12" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2544,34 +2618,34 @@
         <f>IF(OR(AB13="",D13="",D13=0),"",AB13/D13)</f>
         <v/>
       </c>
-      <c r="AP13" t="n">
+      <c r="AP13" s="27" t="n">
         <v>0.03745</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ13" s="27" t="n">
         <v>0.03843</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AR13" s="27" t="n">
         <v>0.03614</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AS13" s="27" t="n">
         <v>0.03737</v>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
+      <c r="AT13" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU13" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
+      <c r="AY13" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ13" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2655,34 +2729,34 @@
         <f>IF(OR(AB14="",D14="",D14=0),"",AB14/D14)</f>
         <v/>
       </c>
-      <c r="AP14" t="n">
+      <c r="AP14" s="27" t="n">
         <v>0.03737</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AQ14" s="27" t="n">
         <v>0.03769</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AR14" s="27" t="n">
         <v>0.03474</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS14" s="27" t="n">
         <v>0.03584</v>
       </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
+      <c r="AT14" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU14" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="AY14" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ14" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2766,34 +2840,34 @@
         <f>IF(OR(AB15="",D15="",D15=0),"",AB15/D15)</f>
         <v/>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP15" s="27" t="n">
         <v>0.03583</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ15" s="27" t="n">
         <v>0.03636</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AR15" s="27" t="n">
         <v>0.03347</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AS15" s="27" t="n">
         <v>0.03595</v>
       </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
+      <c r="AT15" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU15" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
+      <c r="AY15" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ15" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2877,34 +2951,34 @@
         <f>IF(OR(AB16="",D16="",D16=0),"",AB16/D16)</f>
         <v/>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP16" s="27" t="n">
         <v>0.03597</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ16" s="27" t="n">
         <v>0.03801</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR16" s="27" t="n">
         <v>0.0342</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AS16" s="27" t="n">
         <v>0.03466</v>
       </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
+      <c r="AT16" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU16" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
+      <c r="AY16" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ16" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -2988,34 +3062,34 @@
         <f>IF(OR(AB17="",D17="",D17=0),"",AB17/D17)</f>
         <v/>
       </c>
-      <c r="AP17" t="n">
+      <c r="AP17" s="27" t="n">
         <v>0.03466</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ17" s="27" t="n">
         <v>0.0359</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR17" s="27" t="n">
         <v>0.03447</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AS17" s="27" t="n">
         <v>0.03548</v>
       </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
+      <c r="AT17" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU17" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="AY17" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ17" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3099,34 +3173,34 @@
         <f>IF(OR(AB18="",D18="",D18=0),"",AB18/D18)</f>
         <v/>
       </c>
-      <c r="AP18" t="n">
+      <c r="AP18" s="27" t="n">
         <v>0.03547</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AQ18" s="27" t="n">
         <v>0.04045</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AR18" s="27" t="n">
         <v>0.03476</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AS18" s="27" t="n">
         <v>0.03648</v>
       </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
+      <c r="AT18" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU18" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
+      <c r="AY18" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ18" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3210,34 +3284,34 @@
         <f>IF(OR(AB19="",D19="",D19=0),"",AB19/D19)</f>
         <v/>
       </c>
-      <c r="AP19" t="n">
+      <c r="AP19" s="27" t="n">
         <v>0.03651</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ19" s="27" t="n">
         <v>0.04399</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR19" s="27" t="n">
         <v>0.03585</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AS19" s="27" t="n">
         <v>0.04138</v>
       </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
+      <c r="AT19" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU19" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
+      <c r="AY19" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ19" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3321,34 +3395,34 @@
         <f>IF(OR(AB20="",D20="",D20=0),"",AB20/D20)</f>
         <v/>
       </c>
-      <c r="AP20" t="n">
+      <c r="AP20" s="27" t="n">
         <v>0.04138</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ20" s="27" t="n">
         <v>0.0434</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR20" s="27" t="n">
         <v>0.03862</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AS20" s="27" t="n">
         <v>0.041</v>
       </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
+      <c r="AT20" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU20" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="AY20" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ20" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3432,34 +3506,34 @@
         <f>IF(OR(AB21="",D21="",D21=0),"",AB21/D21)</f>
         <v/>
       </c>
-      <c r="AP21" t="n">
+      <c r="AP21" s="27" t="n">
         <v>0.04099</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AQ21" s="27" t="n">
         <v>0.04282</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AR21" s="27" t="n">
         <v>0.03994</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AS21" s="27" t="n">
         <v>0.04231</v>
       </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
+      <c r="AT21" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU21" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="AY21" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ21" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3543,34 +3617,34 @@
         <f>IF(OR(AB22="",D22="",D22=0),"",AB22/D22)</f>
         <v/>
       </c>
-      <c r="AP22" t="n">
+      <c r="AP22" s="27" t="n">
         <v>0.04232</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AQ22" s="27" t="n">
         <v>0.04444</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AR22" s="27" t="n">
         <v>0.04146</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AS22" s="27" t="n">
         <v>0.04412</v>
       </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
+      <c r="AT22" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU22" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="AY22" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ22" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3654,34 +3728,34 @@
         <f>IF(OR(AB23="",D23="",D23=0),"",AB23/D23)</f>
         <v/>
       </c>
-      <c r="AP23" t="n">
+      <c r="AP23" s="27" t="n">
         <v>0.04411</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AQ23" s="27" t="n">
         <v>0.0547</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AR23" s="27" t="n">
         <v>0.0425</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AS23" s="27" t="n">
         <v>0.05111</v>
       </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
+      <c r="AT23" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU23" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="AY23" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ23" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3765,34 +3839,34 @@
         <f>IF(OR(AB24="",D24="",D24=0),"",AB24/D24)</f>
         <v/>
       </c>
-      <c r="AP24" t="n">
+      <c r="AP24" s="27" t="n">
         <v>0.05113</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AQ24" s="27" t="n">
         <v>0.06464</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AR24" s="27" t="n">
         <v>0.05102</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AS24" s="27" t="n">
         <v>0.06121</v>
       </c>
-      <c r="AT24" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU24" t="inlineStr">
+      <c r="AT24" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU24" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ24" t="inlineStr">
+      <c r="AY24" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ24" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3876,34 +3950,34 @@
         <f>IF(OR(AB25="",D25="",D25=0),"",AB25/D25)</f>
         <v/>
       </c>
-      <c r="AP25" t="n">
+      <c r="AP25" s="27" t="n">
         <v>0.06121</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AQ25" s="27" t="n">
         <v>0.08840000000000001</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AR25" s="27" t="n">
         <v>0.04705</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AS25" s="27" t="n">
         <v>0.07048</v>
       </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
+      <c r="AT25" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU25" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
+      <c r="AY25" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ25" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -3987,34 +4061,34 @@
         <f>IF(OR(AB26="",D26="",D26=0),"",AB26/D26)</f>
         <v/>
       </c>
-      <c r="AP26" t="n">
+      <c r="AP26" s="27" t="n">
         <v>0.07049</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AQ26" s="27" t="n">
         <v>0.1223</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AR26" s="27" t="n">
         <v>0.06454</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AS26" s="27" t="n">
         <v>0.11112</v>
       </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU26" t="inlineStr">
+      <c r="AT26" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU26" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ26" t="inlineStr">
+      <c r="AY26" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ26" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4098,34 +4172,34 @@
         <f>IF(OR(AB27="",D27="",D27=0),"",AB27/D27)</f>
         <v/>
       </c>
-      <c r="AP27" t="n">
+      <c r="AP27" s="27" t="n">
         <v>0.11112</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AQ27" s="27" t="n">
         <v>0.23888</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AR27" s="27" t="n">
         <v>0.09421</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AS27" s="27" t="n">
         <v>0.22587</v>
       </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
+      <c r="AT27" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU27" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ27" t="inlineStr">
+      <c r="AY27" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ27" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4209,34 +4283,34 @@
         <f>IF(OR(AB28="",D28="",D28=0),"",AB28/D28)</f>
         <v/>
       </c>
-      <c r="AP28" t="n">
+      <c r="AP28" s="27" t="n">
         <v>0.22591</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AQ28" s="27" t="n">
         <v>0.30843</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AR28" s="27" t="n">
         <v>0.21501</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AS28" s="27" t="n">
         <v>0.26721</v>
       </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU28" t="inlineStr">
+      <c r="AT28" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU28" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ28" t="inlineStr">
+      <c r="AY28" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ28" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4320,34 +4394,34 @@
         <f>IF(OR(AB29="",D29="",D29=0),"",AB29/D29)</f>
         <v/>
       </c>
-      <c r="AP29" t="n">
+      <c r="AP29" s="27" t="n">
         <v>0.2672</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AQ29" s="27" t="n">
         <v>0.33999</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AR29" s="27" t="n">
         <v>0.13123</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AS29" s="27" t="n">
         <v>0.1824</v>
       </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU29" t="inlineStr">
+      <c r="AT29" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU29" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ29" t="inlineStr">
+      <c r="AY29" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ29" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4431,34 +4505,34 @@
         <f>IF(OR(AB30="",D30="",D30=0),"",AB30/D30)</f>
         <v/>
       </c>
-      <c r="AP30" t="n">
+      <c r="AP30" s="27" t="n">
         <v>0.1824</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AQ30" s="27" t="n">
         <v>0.241</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AR30" s="27" t="n">
         <v>0.11758</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AS30" s="27" t="n">
         <v>0.23043</v>
       </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU30" t="inlineStr">
+      <c r="AT30" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU30" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
+      <c r="AY30" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ30" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4542,34 +4616,34 @@
         <f>IF(OR(AB31="",D31="",D31=0),"",AB31/D31)</f>
         <v/>
       </c>
-      <c r="AP31" t="n">
+      <c r="AP31" s="27" t="n">
         <v>0.23048</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AQ31" s="27" t="n">
         <v>0.27999</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AR31" s="27" t="n">
         <v>0.21352</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AS31" s="27" t="n">
         <v>0.27455</v>
       </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU31" t="inlineStr">
+      <c r="AT31" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU31" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ31" t="inlineStr">
+      <c r="AY31" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ31" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4653,34 +4727,34 @@
         <f>IF(OR(AB32="",D32="",D32=0),"",AB32/D32)</f>
         <v/>
       </c>
-      <c r="AP32" t="n">
+      <c r="AP32" s="27" t="n">
         <v>0.27452</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ32" s="27" t="n">
         <v>0.323</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR32" s="27" t="n">
         <v>0.2303</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS32" s="27" t="n">
         <v>0.30136</v>
       </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
+      <c r="AT32" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU32" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ32" t="inlineStr">
+      <c r="AY32" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ32" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4764,34 +4838,34 @@
         <f>IF(OR(AB33="",D33="",D33=0),"",AB33/D33)</f>
         <v/>
       </c>
-      <c r="AP33" t="n">
+      <c r="AP33" s="27" t="n">
         <v>0.30137</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AQ33" s="27" t="n">
         <v>0.39</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AR33" s="27" t="n">
         <v>0.29332</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AS33" s="27" t="n">
         <v>0.34658</v>
       </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU33" t="inlineStr">
+      <c r="AT33" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU33" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ33" t="inlineStr">
+      <c r="AY33" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ33" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -4885,34 +4959,34 @@
           <t>hau-markup, phan phoi dang chay</t>
         </is>
       </c>
-      <c r="AP34" t="n">
+      <c r="AP34" s="27" t="n">
         <v>0.34659</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AQ34" s="27" t="n">
         <v>0.408</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AR34" s="27" t="n">
         <v>0.3401</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AS34" s="27" t="n">
         <v>0.37932</v>
       </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
+      <c r="AT34" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU34" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
+      <c r="AY34" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ34" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5001,34 +5075,34 @@
         <f>IF(OR(AB35="",D35="",D35=0),"",AB35/D35)</f>
         <v/>
       </c>
-      <c r="AP35" t="n">
+      <c r="AP35" s="27" t="n">
         <v>0.37931</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AQ35" s="27" t="n">
         <v>0.67205</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AR35" s="27" t="n">
         <v>0.2601</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AS35" s="27" t="n">
         <v>0.33984</v>
       </c>
-      <c r="AT35" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU35" t="inlineStr">
+      <c r="AT35" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU35" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ35" t="inlineStr">
+      <c r="AY35" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ35" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5127,34 +5201,34 @@
           <t>px -31%, OI -44% — suppressor dung bai</t>
         </is>
       </c>
-      <c r="AP36" t="n">
+      <c r="AP36" s="27" t="n">
         <v>0.33984</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AQ36" s="27" t="n">
         <v>0.3838</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AR36" s="27" t="n">
         <v>0.2025</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AS36" s="27" t="n">
         <v>0.21714</v>
       </c>
-      <c r="AT36" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU36" t="inlineStr">
+      <c r="AT36" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU36" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ36" t="inlineStr">
+      <c r="AY36" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ36" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5238,34 +5312,34 @@
         <f>IF(OR(AB37="",D37="",D37=0),"",AB37/D37)</f>
         <v/>
       </c>
-      <c r="AP37" t="n">
+      <c r="AP37" s="27" t="n">
         <v>0.21714</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AQ37" s="27" t="n">
         <v>0.22437</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AR37" s="27" t="n">
         <v>0.13306</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AS37" s="27" t="n">
         <v>0.17216</v>
       </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU37" t="inlineStr">
+      <c r="AT37" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU37" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ37" t="inlineStr">
+      <c r="AY37" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ37" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5349,34 +5423,34 @@
         <f>IF(OR(AB38="",D38="",D38=0),"",AB38/D38)</f>
         <v/>
       </c>
-      <c r="AP38" t="n">
+      <c r="AP38" s="27" t="n">
         <v>0.17216</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AQ38" s="27" t="n">
         <v>0.2065</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AR38" s="27" t="n">
         <v>0.05417</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AS38" s="27" t="n">
         <v>0.06101</v>
       </c>
-      <c r="AT38" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU38" t="inlineStr">
+      <c r="AT38" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU38" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ38" t="inlineStr">
+      <c r="AY38" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ38" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5460,34 +5534,34 @@
         <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
         <v/>
       </c>
-      <c r="AP39" t="n">
+      <c r="AP39" s="27" t="n">
         <v>0.06101</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AQ39" s="27" t="n">
         <v>0.07698000000000001</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AR39" s="27" t="n">
         <v>0.0529</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AS39" s="27" t="n">
         <v>0.0575</v>
       </c>
-      <c r="AT39" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU39" t="inlineStr">
+      <c r="AT39" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU39" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ39" t="inlineStr">
+      <c r="AY39" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ39" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5558,34 +5632,34 @@
       <c r="AC40" s="27" t="n">
         <v>0.462</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AP40" s="27" t="n">
         <v>0.05749</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AQ40" s="27" t="n">
         <v>0.06766</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AR40" s="27" t="n">
         <v>0.05009</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AS40" s="27" t="n">
         <v>0.05078</v>
       </c>
-      <c r="AT40" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU40" t="inlineStr">
+      <c r="AT40" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU40" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ40" t="inlineStr">
+      <c r="AY40" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ40" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5656,34 +5730,34 @@
       <c r="AC41" s="27" t="n">
         <v>0.493</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AP41" s="27" t="n">
         <v>0.05078</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AQ41" s="27" t="n">
         <v>0.05122</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AR41" s="27" t="n">
         <v>0.04334</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AS41" s="27" t="n">
         <v>0.04469</v>
       </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU41" t="inlineStr">
+      <c r="AT41" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU41" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ41" t="inlineStr">
+      <c r="AY41" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ41" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5754,34 +5828,34 @@
       <c r="AC42" s="27" t="n">
         <v>0.481</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AP42" s="27" t="n">
         <v>0.04469</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AQ42" s="27" t="n">
         <v>0.04652</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AR42" s="27" t="n">
         <v>0.04028</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AS42" s="27" t="n">
         <v>0.04419</v>
       </c>
-      <c r="AT42" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU42" t="inlineStr">
+      <c r="AT42" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU42" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ42" t="inlineStr">
+      <c r="AY42" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ42" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5852,34 +5926,34 @@
       <c r="AC43" s="27" t="n">
         <v>0.483</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AP43" s="27" t="n">
         <v>0.0442</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AQ43" s="27" t="n">
         <v>0.06186</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AR43" s="27" t="n">
         <v>0.0368</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AS43" s="27" t="n">
         <v>0.05244</v>
       </c>
-      <c r="AT43" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU43" t="inlineStr">
+      <c r="AT43" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU43" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ43" t="inlineStr">
+      <c r="AY43" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ43" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -5969,34 +6043,34 @@
       <c r="AM44" s="63" t="n"/>
       <c r="AN44" s="63" t="n"/>
       <c r="AO44" s="63" t="n"/>
-      <c r="AP44" t="n">
+      <c r="AP44" s="27" t="n">
         <v>0.05243</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AQ44" s="27" t="n">
         <v>0.05586</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AR44" s="27" t="n">
         <v>0.0418</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AS44" s="27" t="n">
         <v>0.04311</v>
       </c>
-      <c r="AT44" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU44" t="inlineStr">
+      <c r="AT44" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU44" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ44" t="inlineStr">
+      <c r="AY44" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ44" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6069,34 +6143,34 @@
         <f>IF(OR(AB45="",D45="",D45=0),"",AB45/D45)</f>
         <v/>
       </c>
-      <c r="AP45" t="n">
+      <c r="AP45" s="27" t="n">
         <v>0.0398</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AQ45" s="27" t="n">
         <v>0.0449</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AR45" s="27" t="n">
         <v>0.03658</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AS45" s="27" t="n">
         <v>0.03704</v>
       </c>
-      <c r="AT45" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU45" t="inlineStr">
+      <c r="AT45" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU45" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ45" t="inlineStr">
+      <c r="AY45" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ45" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6169,34 +6243,34 @@
         <f>IF(OR(AB46="",D46="",D46=0),"",AB46/D46)</f>
         <v/>
       </c>
-      <c r="AP46" t="n">
+      <c r="AP46" s="27" t="n">
         <v>0.03932</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AQ46" s="27" t="n">
         <v>0.04029</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AR46" s="27" t="n">
         <v>0.03804</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AS46" s="27" t="n">
         <v>0.03895</v>
       </c>
-      <c r="AT46" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU46" t="inlineStr">
+      <c r="AT46" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU46" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ46" t="inlineStr">
+      <c r="AY46" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ46" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6269,34 +6343,34 @@
         <f>IF(OR(AB47="",D47="",D47=0),"",AB47/D47)</f>
         <v/>
       </c>
-      <c r="AP47" t="n">
+      <c r="AP47" s="27" t="n">
         <v>0.03894</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AQ47" s="27" t="n">
         <v>0.03977</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AR47" s="27" t="n">
         <v>0.03273</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AS47" s="27" t="n">
         <v>0.03633</v>
       </c>
-      <c r="AT47" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU47" t="inlineStr">
+      <c r="AT47" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU47" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ47" t="inlineStr">
+      <c r="AY47" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ47" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6369,34 +6443,34 @@
         <f>IF(OR(AB48="",D48="",D48=0),"",AB48/D48)</f>
         <v/>
       </c>
-      <c r="AP48" t="n">
+      <c r="AP48" s="27" t="n">
         <v>0.03633</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AQ48" s="27" t="n">
         <v>0.04014</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AR48" s="27" t="n">
         <v>0.03395</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AS48" s="27" t="n">
         <v>0.03981</v>
       </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU48" t="inlineStr">
+      <c r="AT48" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU48" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ48" t="inlineStr">
+      <c r="AY48" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ48" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6469,34 +6543,34 @@
         <f>IF(OR(AB49="",D49="",D49=0),"",AB49/D49)</f>
         <v/>
       </c>
-      <c r="AP49" t="n">
+      <c r="AP49" s="27" t="n">
         <v>0.03704</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AQ49" s="27" t="n">
         <v>0.03944</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AR49" s="27" t="n">
         <v>0.03583</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AS49" s="27" t="n">
         <v>0.03821</v>
       </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU49" t="inlineStr">
+      <c r="AT49" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU49" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ49" t="inlineStr">
+      <c r="AY49" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ49" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6569,34 +6643,34 @@
         <f>IF(OR(AB50="",D50="",D50=0),"",AB50/D50)</f>
         <v/>
       </c>
-      <c r="AP50" t="n">
+      <c r="AP50" s="27" t="n">
         <v>0.03821</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AQ50" s="27" t="n">
         <v>0.03919</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AR50" s="27" t="n">
         <v>0.03638</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AS50" s="27" t="n">
         <v>0.03694</v>
       </c>
-      <c r="AT50" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU50" t="inlineStr">
+      <c r="AT50" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU50" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ50" t="inlineStr">
+      <c r="AY50" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ50" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6669,34 +6743,34 @@
         <f>IF(OR(AB51="",D51="",D51=0),"",AB51/D51)</f>
         <v/>
       </c>
-      <c r="AP51" t="n">
+      <c r="AP51" s="27" t="n">
         <v>0.03694</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AQ51" s="27" t="n">
         <v>0.03761</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AR51" s="27" t="n">
         <v>0.03432</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AS51" s="27" t="n">
         <v>0.03514</v>
       </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU51" t="inlineStr">
+      <c r="AT51" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU51" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ51" t="inlineStr">
+      <c r="AY51" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ51" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6729,34 +6803,34 @@
       <c r="I52" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AP52" s="27" t="n">
         <v>0.03774</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AQ52" s="27" t="n">
         <v>0.04296</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AR52" s="27" t="n">
         <v>0.03582</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AS52" s="27" t="n">
         <v>0.04087</v>
       </c>
-      <c r="AT52" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU52" t="inlineStr">
+      <c r="AT52" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU52" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ52" t="inlineStr">
+      <c r="AY52" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ52" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6789,34 +6863,34 @@
       <c r="I53" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AP53" s="27" t="n">
         <v>0.04087</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AQ53" s="27" t="n">
         <v>0.0477</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AR53" s="27" t="n">
         <v>0.0406</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AS53" s="27" t="n">
         <v>0.04741</v>
       </c>
-      <c r="AT53" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU53" t="inlineStr">
+      <c r="AT53" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU53" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ53" t="inlineStr">
+      <c r="AY53" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ53" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6849,34 +6923,34 @@
       <c r="I54" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AP54" s="27" t="n">
         <v>0.04739</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AQ54" s="27" t="n">
         <v>0.0484</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AR54" s="27" t="n">
         <v>0.0368</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AS54" s="27" t="n">
         <v>0.038</v>
       </c>
-      <c r="AT54" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU54" t="inlineStr">
+      <c r="AT54" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU54" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ54" t="inlineStr">
+      <c r="AY54" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ54" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6909,34 +6983,34 @@
       <c r="I55" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AP55" s="27" t="n">
         <v>0.03953</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AQ55" s="27" t="n">
         <v>0.0414</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AR55" s="27" t="n">
         <v>0.03872</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AS55" s="27" t="n">
         <v>0.04073</v>
       </c>
-      <c r="AT55" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU55" t="inlineStr">
+      <c r="AT55" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU55" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ55" t="inlineStr">
+      <c r="AY55" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ55" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -6969,34 +7043,34 @@
       <c r="I56" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AP56" s="27" t="n">
         <v>0.04076</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AQ56" s="27" t="n">
         <v>0.04128</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AR56" s="27" t="n">
         <v>0.03982</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AS56" s="27" t="n">
         <v>0.04084</v>
       </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU56" t="inlineStr">
+      <c r="AT56" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU56" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ56" t="inlineStr">
+      <c r="AY56" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ56" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7029,34 +7103,34 @@
       <c r="I57" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AP57" s="27" t="n">
         <v>0.04085</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AQ57" s="27" t="n">
         <v>0.04368</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AR57" s="27" t="n">
         <v>0.03957</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AS57" s="27" t="n">
         <v>0.04123</v>
       </c>
-      <c r="AT57" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU57" t="inlineStr">
+      <c r="AT57" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU57" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ57" t="inlineStr">
+      <c r="AY57" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ57" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7089,34 +7163,34 @@
       <c r="I58" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AP58" s="27" t="n">
         <v>0.04124</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AQ58" s="27" t="n">
         <v>0.04226</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AR58" s="27" t="n">
         <v>0.03898</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AS58" s="27" t="n">
         <v>0.03963</v>
       </c>
-      <c r="AT58" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU58" t="inlineStr">
+      <c r="AT58" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU58" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ58" t="inlineStr">
+      <c r="AY58" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ58" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7149,34 +7223,34 @@
       <c r="I59" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AP59" s="27" t="n">
         <v>0.03966</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AQ59" s="27" t="n">
         <v>0.04026</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AR59" s="27" t="n">
         <v>0.03625</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AS59" s="27" t="n">
         <v>0.03668</v>
       </c>
-      <c r="AT59" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU59" t="inlineStr">
+      <c r="AT59" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU59" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ59" t="inlineStr">
+      <c r="AY59" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ59" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7209,34 +7283,34 @@
       <c r="I60" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AP60" s="27" t="n">
         <v>0.03669</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AQ60" s="27" t="n">
         <v>0.04178</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AR60" s="27" t="n">
         <v>0.03636</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AS60" s="27" t="n">
         <v>0.03965</v>
       </c>
-      <c r="AT60" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU60" t="inlineStr">
+      <c r="AT60" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU60" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ60" t="inlineStr">
+      <c r="AY60" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ60" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7269,34 +7343,34 @@
       <c r="I61" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP61" t="n">
+      <c r="AP61" s="27" t="n">
         <v>0.03964</v>
       </c>
-      <c r="AQ61" t="n">
+      <c r="AQ61" s="27" t="n">
         <v>0.04064</v>
       </c>
-      <c r="AR61" t="n">
+      <c r="AR61" s="27" t="n">
         <v>0.03855</v>
       </c>
-      <c r="AS61" t="n">
+      <c r="AS61" s="27" t="n">
         <v>0.03883</v>
       </c>
-      <c r="AT61" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU61" t="inlineStr">
+      <c r="AT61" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU61" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ61" t="inlineStr">
+      <c r="AY61" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ61" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7329,34 +7403,34 @@
       <c r="I62" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP62" t="n">
+      <c r="AP62" s="27" t="n">
         <v>0.03884</v>
       </c>
-      <c r="AQ62" t="n">
+      <c r="AQ62" s="27" t="n">
         <v>0.03896</v>
       </c>
-      <c r="AR62" t="n">
+      <c r="AR62" s="27" t="n">
         <v>0.03739</v>
       </c>
-      <c r="AS62" t="n">
+      <c r="AS62" s="27" t="n">
         <v>0.03768</v>
       </c>
-      <c r="AT62" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU62" t="inlineStr">
+      <c r="AT62" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU62" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ62" t="inlineStr">
+      <c r="AY62" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ62" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7389,34 +7463,34 @@
       <c r="I63" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP63" t="n">
+      <c r="AP63" s="27" t="n">
         <v>0.03768</v>
       </c>
-      <c r="AQ63" t="n">
+      <c r="AQ63" s="27" t="n">
         <v>0.03882</v>
       </c>
-      <c r="AR63" t="n">
+      <c r="AR63" s="27" t="n">
         <v>0.03654</v>
       </c>
-      <c r="AS63" t="n">
+      <c r="AS63" s="27" t="n">
         <v>0.03762</v>
       </c>
-      <c r="AT63" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU63" t="inlineStr">
+      <c r="AT63" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU63" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ63" t="inlineStr">
+      <c r="AY63" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ63" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7449,34 +7523,34 @@
       <c r="I64" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP64" t="n">
+      <c r="AP64" s="27" t="n">
         <v>0.0376</v>
       </c>
-      <c r="AQ64" t="n">
+      <c r="AQ64" s="27" t="n">
         <v>0.0388</v>
       </c>
-      <c r="AR64" t="n">
+      <c r="AR64" s="27" t="n">
         <v>0.036</v>
       </c>
-      <c r="AS64" t="n">
+      <c r="AS64" s="27" t="n">
         <v>0.03875</v>
       </c>
-      <c r="AT64" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU64" t="inlineStr">
+      <c r="AT64" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU64" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ64" t="inlineStr">
+      <c r="AY64" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ64" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7509,34 +7583,34 @@
       <c r="I65" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="AP65" t="n">
+      <c r="AP65" s="27" t="n">
         <v>0.03874</v>
       </c>
-      <c r="AQ65" t="n">
+      <c r="AQ65" s="27" t="n">
         <v>0.04046</v>
       </c>
-      <c r="AR65" t="n">
+      <c r="AR65" s="27" t="n">
         <v>0.03643</v>
       </c>
-      <c r="AS65" t="n">
+      <c r="AS65" s="27" t="n">
         <v>0.03708</v>
       </c>
-      <c r="AT65" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU65" t="inlineStr">
+      <c r="AT65" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU65" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ65" t="inlineStr">
+      <c r="AY65" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ65" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7569,34 +7643,34 @@
       <c r="I66" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP66" t="n">
+      <c r="AP66" s="27" t="n">
         <v>0.03708</v>
       </c>
-      <c r="AQ66" t="n">
+      <c r="AQ66" s="27" t="n">
         <v>0.03782</v>
       </c>
-      <c r="AR66" t="n">
+      <c r="AR66" s="27" t="n">
         <v>0.0351</v>
       </c>
-      <c r="AS66" t="n">
+      <c r="AS66" s="27" t="n">
         <v>0.03718</v>
       </c>
-      <c r="AT66" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU66" t="inlineStr">
+      <c r="AT66" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU66" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ66" t="inlineStr">
+      <c r="AY66" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ66" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7629,34 +7703,34 @@
       <c r="I67" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="AP67" t="n">
+      <c r="AP67" s="27" t="n">
         <v>0.03718</v>
       </c>
-      <c r="AQ67" t="n">
+      <c r="AQ67" s="27" t="n">
         <v>0.03931</v>
       </c>
-      <c r="AR67" t="n">
+      <c r="AR67" s="27" t="n">
         <v>0.03641</v>
       </c>
-      <c r="AS67" t="n">
+      <c r="AS67" s="27" t="n">
         <v>0.0375</v>
       </c>
-      <c r="AT67" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU67" t="inlineStr">
+      <c r="AT67" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU67" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ67" t="inlineStr">
+      <c r="AY67" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ67" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7701,34 +7775,34 @@
       <c r="Q68" s="27" t="n">
         <v>1.4919</v>
       </c>
-      <c r="AP68" t="n">
+      <c r="AP68" s="27" t="n">
         <v>0.04312</v>
       </c>
-      <c r="AQ68" t="n">
+      <c r="AQ68" s="27" t="n">
         <v>0.04623</v>
       </c>
-      <c r="AR68" t="n">
+      <c r="AR68" s="27" t="n">
         <v>0.04025</v>
       </c>
-      <c r="AS68" t="n">
+      <c r="AS68" s="27" t="n">
         <v>0.04376</v>
       </c>
-      <c r="AT68" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU68" t="inlineStr">
+      <c r="AT68" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU68" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ68" t="inlineStr">
+      <c r="AY68" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ68" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7773,34 +7847,34 @@
       <c r="Q69" s="27" t="n">
         <v>1.5445</v>
       </c>
-      <c r="AP69" t="n">
+      <c r="AP69" s="27" t="n">
         <v>0.04376</v>
       </c>
-      <c r="AQ69" t="n">
+      <c r="AQ69" s="27" t="n">
         <v>0.04422</v>
       </c>
-      <c r="AR69" t="n">
+      <c r="AR69" s="27" t="n">
         <v>0.03906</v>
       </c>
-      <c r="AS69" t="n">
+      <c r="AS69" s="27" t="n">
         <v>0.04068</v>
       </c>
-      <c r="AT69" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU69" t="inlineStr">
+      <c r="AT69" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU69" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ69" t="inlineStr">
+      <c r="AY69" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ69" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7845,34 +7919,34 @@
       <c r="Q70" s="27" t="n">
         <v>1.5893</v>
       </c>
-      <c r="AP70" t="n">
+      <c r="AP70" s="27" t="n">
         <v>0.04067</v>
       </c>
-      <c r="AQ70" t="n">
+      <c r="AQ70" s="27" t="n">
         <v>0.0415</v>
       </c>
-      <c r="AR70" t="n">
+      <c r="AR70" s="27" t="n">
         <v>0.03832</v>
       </c>
-      <c r="AS70" t="n">
+      <c r="AS70" s="27" t="n">
         <v>0.04011</v>
       </c>
-      <c r="AT70" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU70" t="inlineStr">
+      <c r="AT70" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU70" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ70" t="inlineStr">
+      <c r="AY70" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ70" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7917,34 +7991,34 @@
       <c r="Q71" s="27" t="n">
         <v>1.5151</v>
       </c>
-      <c r="AP71" t="n">
+      <c r="AP71" s="27" t="n">
         <v>0.04011</v>
       </c>
-      <c r="AQ71" t="n">
+      <c r="AQ71" s="27" t="n">
         <v>0.04709</v>
       </c>
-      <c r="AR71" t="n">
+      <c r="AR71" s="27" t="n">
         <v>0.03529</v>
       </c>
-      <c r="AS71" t="n">
+      <c r="AS71" s="27" t="n">
         <v>0.03932</v>
       </c>
-      <c r="AT71" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU71" t="inlineStr">
+      <c r="AT71" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU71" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ71" t="inlineStr">
+      <c r="AY71" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ71" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -7989,34 +8063,34 @@
       <c r="Q72" s="27" t="n">
         <v>1.3969</v>
       </c>
-      <c r="AP72" t="n">
+      <c r="AP72" s="27" t="n">
         <v>0.03515</v>
       </c>
-      <c r="AQ72" t="n">
+      <c r="AQ72" s="27" t="n">
         <v>0.0367</v>
       </c>
-      <c r="AR72" t="n">
+      <c r="AR72" s="27" t="n">
         <v>0.03497</v>
       </c>
-      <c r="AS72" t="n">
+      <c r="AS72" s="27" t="n">
         <v>0.0356</v>
       </c>
-      <c r="AT72" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU72" t="inlineStr">
+      <c r="AT72" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU72" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ72" t="inlineStr">
+      <c r="AY72" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ72" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -8061,34 +8135,34 @@
       <c r="Q73" s="27" t="n">
         <v>1.3485</v>
       </c>
-      <c r="AP73" t="n">
+      <c r="AP73" s="27" t="n">
         <v>0.03561</v>
       </c>
-      <c r="AQ73" t="n">
+      <c r="AQ73" s="27" t="n">
         <v>0.03798</v>
       </c>
-      <c r="AR73" t="n">
+      <c r="AR73" s="27" t="n">
         <v>0.03455</v>
       </c>
-      <c r="AS73" t="n">
+      <c r="AS73" s="27" t="n">
         <v>0.03653</v>
       </c>
-      <c r="AT73" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU73" t="inlineStr">
+      <c r="AT73" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU73" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="AY73" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ73" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -8133,34 +8207,34 @@
       <c r="Q74" s="27" t="n">
         <v>1.3579</v>
       </c>
-      <c r="AP74" t="n">
+      <c r="AP74" s="27" t="n">
         <v>0.03653</v>
       </c>
-      <c r="AQ74" t="n">
+      <c r="AQ74" s="27" t="n">
         <v>0.03751</v>
       </c>
-      <c r="AR74" t="n">
+      <c r="AR74" s="27" t="n">
         <v>0.03511</v>
       </c>
-      <c r="AS74" t="n">
+      <c r="AS74" s="27" t="n">
         <v>0.03571</v>
       </c>
-      <c r="AT74" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU74" t="inlineStr">
+      <c r="AT74" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU74" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ74" t="inlineStr">
+      <c r="AY74" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ74" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
@@ -8205,34 +8279,34 @@
       <c r="Q75" s="27" t="n">
         <v>1.3196</v>
       </c>
-      <c r="AP75" t="n">
+      <c r="AP75" s="27" t="n">
         <v>0.0357</v>
       </c>
-      <c r="AQ75" t="n">
+      <c r="AQ75" s="27" t="n">
         <v>0.03691</v>
       </c>
-      <c r="AR75" t="n">
+      <c r="AR75" s="27" t="n">
         <v>0.03546</v>
       </c>
-      <c r="AS75" t="n">
+      <c r="AS75" s="27" t="n">
         <v>0.03646</v>
       </c>
-      <c r="AT75" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AU75" t="inlineStr">
+      <c r="AT75" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU75" s="27" t="inlineStr">
         <is>
           <t>ABSTAIN-STRUCTURAL</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>CHƯA-TRA</t>
-        </is>
-      </c>
-      <c r="AZ75" t="inlineStr">
+      <c r="AY75" s="27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ75" s="27" t="inlineStr">
         <is>
           <t>CHƯA-TRA</t>
         </is>
